--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B4FD901-E1DF-4474-A3E4-41982E58D36A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA2503E-AB61-43DA-893A-6027BB923DA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1006" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1018" uniqueCount="434">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1335,6 +1335,15 @@
   </si>
   <si>
     <t>Inv-148</t>
+  </si>
+  <si>
+    <t>عصايا  500 حجم 120سم 500 90 سم 2 ابريق ماء 8 لتر</t>
+  </si>
+  <si>
+    <t>Inv-149</t>
+  </si>
+  <si>
+    <t>فيتامين حديد</t>
   </si>
 </sst>
 </file>
@@ -2537,6 +2546,15 @@
     <xf numFmtId="165" fontId="16" fillId="18" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2561,23 +2579,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2940,7 +2949,7 @@
       <c r="E2" s="153"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>336.29500000000007</v>
+        <v>606.79500000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7532,81 +7541,81 @@
       </c>
     </row>
     <row r="181" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="142" t="str">
+      <c r="A181" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(176,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B181" s="122" t="str">
+        <v>46277</v>
+      </c>
+      <c r="B181" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(176,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C181" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(176,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D181" s="123" t="str">
+        <v>عصايا  500 حجم 120سم 500 90 سم 2 ابريق ماء 8 لتر</v>
+      </c>
+      <c r="D181" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(176,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E181" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E181" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(176,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F181" s="125" t="str">
+        <v>34.5</v>
+      </c>
+      <c r="F181" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>301.79500000000007</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="142" t="str">
+      <c r="A182" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(177,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>46278</v>
       </c>
       <c r="B182" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(177,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>Inv-149</v>
       </c>
       <c r="C182" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(177,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D182" s="123" t="str">
+        <v>زهور التهاني</v>
+      </c>
+      <c r="D182" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(177,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E182" s="124" t="str">
+        <v>310</v>
+      </c>
+      <c r="E182" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(177,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F182" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F182" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>611.79500000000007</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="142" t="str">
+      <c r="A183" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$204,MATCH(178,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B183" s="122" t="str">
+        <v>46278</v>
+      </c>
+      <c r="B183" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$204,MATCH(178,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C183" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$204,MATCH(178,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D183" s="123" t="str">
+        <v>فيتامين حديد</v>
+      </c>
+      <c r="D183" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(178,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E183" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E183" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(178,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F183" s="125" t="str">
+        <v>5</v>
+      </c>
+      <c r="F183" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>606.79500000000007</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8189,15 +8198,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>2153.19</v>
+        <v>2463.19</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1816.895</v>
+        <v>1856.395</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>336.29500000000007</v>
+        <v>606.79500000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -20305,7 +20314,7 @@
         <v>15</v>
       </c>
       <c r="F189" s="30" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="G189" s="31"/>
       <c r="H189" s="32" t="s">
@@ -20316,7 +20325,7 @@
         <f>IF(AND(D189="",E189="",A189="",B189="",C189=""),"", IFERROR(IF(J188="",D2,J188),D2)+IF(E189="",0,E189)-IF(OR(G189="أبو اسحاق",G189="أبو آدم",G189="أبو اسحاق ",G189="أبو آدم "),0,IF(D189="",0,D189)))</f>
         <v>248.79500000000004</v>
       </c>
-      <c r="K189" s="177" t="s">
+      <c r="K189" s="166" t="s">
         <v>419</v>
       </c>
       <c r="L189">
@@ -20359,7 +20368,7 @@
         <v>20</v>
       </c>
       <c r="F190" s="136" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="G190" s="40"/>
       <c r="H190" s="41" t="s">
@@ -20370,7 +20379,7 @@
         <f>IF(AND(D190="",E190="",A190="",B190="",C190=""),"", IFERROR(IF(J189="",D2,J189),D2)+IF(E190="",0,E190)-IF(OR(G190="أبو اسحاق",G190="أبو آدم",G190="أبو اسحاق ",G190="أبو آدم "),0,IF(D190="",0,D190)))</f>
         <v>268.79500000000007</v>
       </c>
-      <c r="K190" s="178"/>
+      <c r="K190" s="167"/>
       <c r="L190">
         <f>IF(E189&gt;0,COUNTIF($E$4:E189,"&gt;0"),"")</f>
         <v>124</v>
@@ -20411,7 +20420,7 @@
         <v>35</v>
       </c>
       <c r="F191" s="30" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="G191" s="31"/>
       <c r="H191" s="32" t="s">
@@ -20422,7 +20431,7 @@
         <f>IF(AND(D191="",E191="",A191="",B191="",C191=""),"", IFERROR(IF(J190="",D2,J190),D2)+IF(E191="",0,E191)-IF(OR(G191="أبو اسحاق",G191="أبو آدم",G191="أبو اسحاق ",G191="أبو آدم "),0,IF(D191="",0,D191)))</f>
         <v>303.79500000000007</v>
       </c>
-      <c r="K191" s="178"/>
+      <c r="K191" s="167"/>
       <c r="L191">
         <f>IF(E190&gt;0,COUNTIF($E$4:E190,"&gt;0"),"")</f>
         <v>125</v>
@@ -20463,7 +20472,7 @@
         <v>5</v>
       </c>
       <c r="F192" s="136" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="G192" s="40"/>
       <c r="H192" s="41" t="s">
@@ -20474,7 +20483,7 @@
         <f>IF(AND(D192="",E192="",A192="",B192="",C192=""),"", IFERROR(IF(J191="",D2,J191),D2)+IF(E192="",0,E192)-IF(OR(G192="أبو اسحاق",G192="أبو آدم",G192="أبو اسحاق ",G192="أبو آدم "),0,IF(D192="",0,D192)))</f>
         <v>308.79500000000007</v>
       </c>
-      <c r="K192" s="178"/>
+      <c r="K192" s="167"/>
       <c r="L192">
         <f>IF(E191&gt;0,COUNTIF($E$4:E191,"&gt;0"),"")</f>
         <v>126</v>
@@ -20515,7 +20524,7 @@
         <v>7.5</v>
       </c>
       <c r="F193" s="30" t="s">
-        <v>38</v>
+        <v>172</v>
       </c>
       <c r="G193" s="31"/>
       <c r="H193" s="32" t="s">
@@ -20526,7 +20535,7 @@
         <f>IF(AND(D193="",E193="",A193="",B193="",C193=""),"", IFERROR(IF(J192="",D2,J192),D2)+IF(E193="",0,E193)-IF(OR(G193="أبو اسحاق",G193="أبو آدم",G193="أبو اسحاق ",G193="أبو آدم "),0,IF(D193="",0,D193)))</f>
         <v>316.29500000000007</v>
       </c>
-      <c r="K193" s="179"/>
+      <c r="K193" s="168"/>
       <c r="L193">
         <f>IF(E192&gt;0,COUNTIF($E$4:E192,"&gt;0"),"")</f>
         <v>127</v>
@@ -20865,18 +20874,30 @@
       </c>
     </row>
     <row r="200" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="139"/>
+      <c r="A200" s="139">
+        <v>46277</v>
+      </c>
       <c r="B200" s="36"/>
-      <c r="C200" s="37"/>
-      <c r="D200" s="38"/>
+      <c r="C200" s="37" t="s">
+        <v>431</v>
+      </c>
+      <c r="D200" s="38">
+        <v>34.5</v>
+      </c>
       <c r="E200" s="39"/>
-      <c r="F200" s="136"/>
-      <c r="G200" s="40"/>
-      <c r="H200" s="41"/>
+      <c r="F200" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G200" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H200" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I200" s="42"/>
-      <c r="J200" s="43" t="str">
+      <c r="J200" s="43">
         <f>IF(AND(D200="",E200="",A200="",B200="",C200=""),"", IFERROR(IF(J199="",D2,J199),D2)+IF(E200="",0,E200)-IF(OR(G200="أبو اسحاق",G200="أبو آدم",G200="أبو اسحاق ",G200="أبو آدم "),0,IF(D200="",0,D200)))</f>
-        <v/>
+        <v>301.79500000000007</v>
       </c>
       <c r="K200" s="44"/>
       <c r="L200">
@@ -20895,9 +20916,9 @@
         <f>IF(AND(D199&gt;0,F199="أحد الشركاء"),COUNTIFS($D$4:D199,"&gt;"&amp;0,$F$4:F199,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P200" t="str">
+      <c r="P200">
         <f>IF(OR($A200="",$F200="أحد الشركاء",AND($D200="",$E200="")),"",SUMPRODUCT(($A$4:$A200&lt;&gt;"")*($F$4:$F200&lt;&gt;"أحد الشركاء")*((($D$4:$D200&lt;&gt;"")+($E$4:$E200&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>176</v>
       </c>
       <c r="Q200" t="str">
         <f>IF(OR($A200="",$F200&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A200,"&lt;&gt;",$F$4:F200,"أحد الشركاء"))</f>
@@ -20905,27 +20926,39 @@
       </c>
     </row>
     <row r="201" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="25"/>
-      <c r="B201" s="26"/>
-      <c r="C201" s="27"/>
+      <c r="A201" s="25">
+        <v>46278</v>
+      </c>
+      <c r="B201" s="36" t="s">
+        <v>432</v>
+      </c>
+      <c r="C201" s="27" t="s">
+        <v>399</v>
+      </c>
       <c r="D201" s="28"/>
-      <c r="E201" s="29"/>
-      <c r="F201" s="30"/>
+      <c r="E201" s="29">
+        <v>310</v>
+      </c>
+      <c r="F201" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G201" s="31"/>
-      <c r="H201" s="32"/>
+      <c r="H201" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I201" s="33"/>
-      <c r="J201" s="34" t="str">
+      <c r="J201" s="34">
         <f>IF(AND(D201="",E201="",A201="",B201="",C201=""),"", IFERROR(IF(J200="",D2,J200),D2)+IF(E201="",0,E201)-IF(OR(G201="أبو اسحاق",G201="أبو آدم",G201="أبو اسحاق ",G201="أبو آدم "),0,IF(D201="",0,D201)))</f>
-        <v/>
+        <v>611.79500000000007</v>
       </c>
       <c r="K201" s="35"/>
       <c r="L201" t="str">
         <f>IF(E200&gt;0,COUNTIF($E$4:E200,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M201" t="str">
+      <c r="M201">
         <f>IF(AND(D200&gt;0,G200="المحفظة"),COUNTIFS($D$4:D200,"&gt;"&amp;0,$G$4:G200,"المحفظة"),"")</f>
-        <v/>
+        <v>41</v>
       </c>
       <c r="N201" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A201)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A201)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A201&lt;&gt;""),IFERROR(MAX($N$4:N200),0)+1,"")</f>
@@ -20935,9 +20968,9 @@
         <f>IF(AND(D200&gt;0,F200="أحد الشركاء"),COUNTIFS($D$4:D200,"&gt;"&amp;0,$F$4:F200,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P201" t="str">
+      <c r="P201">
         <f>IF(OR($A201="",$F201="أحد الشركاء",AND($D201="",$E201="")),"",SUMPRODUCT(($A$4:$A201&lt;&gt;"")*($F$4:$F201&lt;&gt;"أحد الشركاء")*((($D$4:$D201&lt;&gt;"")+($E$4:$E201&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>177</v>
       </c>
       <c r="Q201" t="str">
         <f>IF(OR($A201="",$F201&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A201,"&lt;&gt;",$F$4:F201,"أحد الشركاء"))</f>
@@ -20945,23 +20978,35 @@
       </c>
     </row>
     <row r="202" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="139"/>
+      <c r="A202" s="139">
+        <v>46278</v>
+      </c>
       <c r="B202" s="36"/>
-      <c r="C202" s="37"/>
-      <c r="D202" s="38"/>
+      <c r="C202" s="37" t="s">
+        <v>433</v>
+      </c>
+      <c r="D202" s="38">
+        <v>5</v>
+      </c>
       <c r="E202" s="39"/>
-      <c r="F202" s="136"/>
-      <c r="G202" s="40"/>
-      <c r="H202" s="41"/>
+      <c r="F202" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G202" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H202" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I202" s="42"/>
-      <c r="J202" s="43" t="str">
+      <c r="J202" s="43">
         <f>IF(AND(D202="",E202="",A202="",B202="",C202=""),"", IFERROR(IF(J201="",D2,J201),D2)+IF(E202="",0,E202)-IF(OR(G202="أبو اسحاق",G202="أبو آدم",G202="أبو اسحاق ",G202="أبو آدم "),0,IF(D202="",0,D202)))</f>
-        <v/>
+        <v>606.79500000000007</v>
       </c>
       <c r="K202" s="44"/>
-      <c r="L202" t="str">
+      <c r="L202">
         <f>IF(E201&gt;0,COUNTIF($E$4:E201,"&gt;0"),"")</f>
-        <v/>
+        <v>135</v>
       </c>
       <c r="M202" t="str">
         <f>IF(AND(D201&gt;0,G201="المحفظة"),COUNTIFS($D$4:D201,"&gt;"&amp;0,$G$4:G201,"المحفظة"),"")</f>
@@ -20975,9 +21020,9 @@
         <f>IF(AND(D201&gt;0,F201="أحد الشركاء"),COUNTIFS($D$4:D201,"&gt;"&amp;0,$F$4:F201,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P202" t="str">
+      <c r="P202">
         <f>IF(OR($A202="",$F202="أحد الشركاء",AND($D202="",$E202="")),"",SUMPRODUCT(($A$4:$A202&lt;&gt;"")*($F$4:$F202&lt;&gt;"أحد الشركاء")*((($D$4:$D202&lt;&gt;"")+($E$4:$E202&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>178</v>
       </c>
       <c r="Q202" t="str">
         <f>IF(OR($A202="",$F202&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A202,"&lt;&gt;",$F$4:F202,"أحد الشركاء"))</f>
@@ -21003,9 +21048,9 @@
         <f>IF(E202&gt;0,COUNTIF($E$4:E202,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M203" t="str">
+      <c r="M203">
         <f>IF(AND(D202&gt;0,G202="المحفظة"),COUNTIFS($D$4:D202,"&gt;"&amp;0,$G$4:G202,"المحفظة"),"")</f>
-        <v/>
+        <v>42</v>
       </c>
       <c r="N203" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A203)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A203)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A203&lt;&gt;""),IFERROR(MAX($N$4:N202),0)+1,"")</f>
@@ -21072,11 +21117,11 @@
       <c r="C205" s="137"/>
       <c r="D205" s="46">
         <f>SUM(D4:D203)</f>
-        <v>3598.3950000000004</v>
+        <v>3637.8950000000004</v>
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>2153.19</v>
+        <v>2463.19</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -21168,7 +21213,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="166" t="s">
+      <c r="A1" s="169" t="s">
         <v>220</v>
       </c>
       <c r="B1" s="159"/>
@@ -21330,13 +21375,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="171" t="s">
         <v>236</v>
       </c>
       <c r="B1" s="159"/>
     </row>
     <row r="2" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="167" t="s">
+      <c r="A2" s="170" t="s">
         <v>237</v>
       </c>
       <c r="B2" s="159"/>
@@ -21358,7 +21403,7 @@
       </c>
     </row>
     <row r="5" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="167" t="s">
+      <c r="A5" s="170" t="s">
         <v>242</v>
       </c>
       <c r="B5" s="159"/>
@@ -21404,7 +21449,7 @@
       </c>
     </row>
     <row r="11" spans="1:2" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="167" t="s">
+      <c r="A11" s="170" t="s">
         <v>251</v>
       </c>
       <c r="B11" s="159"/>
@@ -21487,19 +21532,19 @@
       <c r="K1" s="159"/>
     </row>
     <row r="2" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="169"/>
+      <c r="A2" s="172"/>
       <c r="B2" s="159"/>
       <c r="C2" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="169">
+      <c r="D2" s="172">
         <v>2026</v>
       </c>
       <c r="E2" s="159"/>
       <c r="F2" s="56" t="s">
         <v>256</v>
       </c>
-      <c r="G2" s="172" t="s">
+      <c r="G2" s="175" t="s">
         <v>257</v>
       </c>
       <c r="H2" s="163"/>
@@ -21508,7 +21553,7 @@
       <c r="K2" s="163"/>
     </row>
     <row r="3" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="176" t="s">
         <v>258</v>
       </c>
       <c r="B3" s="159"/>
@@ -28445,7 +28490,7 @@
       </c>
     </row>
     <row r="155" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="170" t="s">
+      <c r="A155" s="173" t="s">
         <v>265</v>
       </c>
       <c r="B155" s="159"/>
@@ -28458,7 +28503,7 @@
         <f>SUM(E5:E154)</f>
         <v>602.5</v>
       </c>
-      <c r="F155" s="171">
+      <c r="F155" s="174">
         <f>COUNTIF(H5:H154,"معلق")</f>
         <v>0</v>
       </c>
@@ -28557,14 +28602,14 @@
       <c r="G1" s="159"/>
     </row>
     <row r="2" spans="1:7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="169" t="s">
+      <c r="A2" s="172" t="s">
         <v>269</v>
       </c>
       <c r="B2" s="159"/>
       <c r="C2" s="56" t="s">
         <v>342</v>
       </c>
-      <c r="D2" s="169" t="s">
+      <c r="D2" s="172" t="s">
         <v>270</v>
       </c>
       <c r="E2" s="159"/>
@@ -28573,7 +28618,7 @@
       </c>
     </row>
     <row r="3" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="173" t="s">
+      <c r="A3" s="176" t="s">
         <v>271</v>
       </c>
       <c r="B3" s="159"/>
@@ -28581,7 +28626,7 @@
         <f>المحفظة!$D$2</f>
         <v>0</v>
       </c>
-      <c r="D3" s="173" t="s">
+      <c r="D3" s="176" t="s">
         <v>272</v>
       </c>
       <c r="E3" s="159"/>
@@ -28591,7 +28636,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="174" t="s">
+      <c r="A4" s="178" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="159"/>
@@ -29902,7 +29947,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="174" t="s">
+      <c r="A55" s="178" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="159"/>
@@ -29916,7 +29961,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="176" t="s">
+      <c r="A56" s="177" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="159"/>
@@ -31227,7 +31272,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="176" t="s">
+      <c r="A107" s="177" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="159"/>
@@ -31241,7 +31286,7 @@
       <c r="G107" s="76"/>
     </row>
     <row r="108" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="170" t="s">
+      <c r="A108" s="173" t="s">
         <v>277</v>
       </c>
       <c r="B108" s="159"/>
@@ -31250,7 +31295,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="175">
+      <c r="E108" s="179">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -31259,17 +31304,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BA2503E-AB61-43DA-893A-6027BB923DA2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE2F4611-2376-48B1-AEFA-82DCD76C6B1C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1301,9 +1301,6 @@
     <t>عطره العدد 10 الحبه .750</t>
   </si>
   <si>
-    <t>لم يدفع</t>
-  </si>
-  <si>
     <t>Inv-143</t>
   </si>
   <si>
@@ -1344,6 +1341,9 @@
   </si>
   <si>
     <t>فيتامين حديد</t>
+  </si>
+  <si>
+    <t>142 السعر الأصلي 7.500 ولكن تم عمله 10 لان نزمول باع شي اخر بقيمه2.5</t>
   </si>
 </sst>
 </file>
@@ -2579,14 +2579,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2949,7 +2949,7 @@
       <c r="E2" s="153"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>606.79500000000007</v>
+        <v>609.29500000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="D174" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$204,MATCH(169,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="E174" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$204,MATCH(169,'كشف الحساب'!$P$4:$P$204,0)),"")</f>
@@ -7381,7 +7381,7 @@
       </c>
       <c r="F174" s="125">
         <f t="shared" si="5"/>
-        <v>316.29500000000007</v>
+        <v>318.79500000000007</v>
       </c>
     </row>
     <row r="175" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7407,7 +7407,7 @@
       </c>
       <c r="F175" s="125">
         <f t="shared" si="5"/>
-        <v>322.29500000000007</v>
+        <v>324.79500000000007</v>
       </c>
     </row>
     <row r="176" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="F176" s="125">
         <f t="shared" si="5"/>
-        <v>324.29500000000007</v>
+        <v>326.79500000000007</v>
       </c>
     </row>
     <row r="177" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="F177" s="125">
         <f t="shared" si="5"/>
-        <v>329.29500000000007</v>
+        <v>331.79500000000007</v>
       </c>
     </row>
     <row r="178" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7485,7 +7485,7 @@
       </c>
       <c r="F178" s="125">
         <f t="shared" si="5"/>
-        <v>331.29500000000007</v>
+        <v>333.79500000000007</v>
       </c>
     </row>
     <row r="179" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7511,7 +7511,7 @@
       </c>
       <c r="F179" s="125">
         <f t="shared" si="5"/>
-        <v>334.29500000000007</v>
+        <v>336.79500000000007</v>
       </c>
     </row>
     <row r="180" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="F180" s="125">
         <f t="shared" si="5"/>
-        <v>336.29500000000007</v>
+        <v>338.79500000000007</v>
       </c>
     </row>
     <row r="181" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7563,7 +7563,7 @@
       </c>
       <c r="F181" s="125">
         <f t="shared" si="5"/>
-        <v>301.79500000000007</v>
+        <v>304.29500000000007</v>
       </c>
     </row>
     <row r="182" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7589,7 +7589,7 @@
       </c>
       <c r="F182" s="125">
         <f t="shared" si="5"/>
-        <v>611.79500000000007</v>
+        <v>614.29500000000007</v>
       </c>
     </row>
     <row r="183" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7615,7 +7615,7 @@
       </c>
       <c r="F183" s="125">
         <f t="shared" si="5"/>
-        <v>606.79500000000007</v>
+        <v>609.29500000000007</v>
       </c>
     </row>
     <row r="184" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8198,7 +8198,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>2463.19</v>
+        <v>2465.69</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -8206,7 +8206,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>606.79500000000007</v>
+        <v>609.29500000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -20326,7 +20326,7 @@
         <v>248.79500000000004</v>
       </c>
       <c r="K189" s="166" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="L189">
         <f>IF(E188&gt;0,COUNTIF($E$4:E188,"&gt;0"),"")</f>
@@ -20521,7 +20521,7 @@
       </c>
       <c r="D193" s="28"/>
       <c r="E193" s="29">
-        <v>7.5</v>
+        <v>10</v>
       </c>
       <c r="F193" s="30" t="s">
         <v>172</v>
@@ -20533,7 +20533,7 @@
       <c r="I193" s="33"/>
       <c r="J193" s="34">
         <f>IF(AND(D193="",E193="",A193="",B193="",C193=""),"", IFERROR(IF(J192="",D2,J192),D2)+IF(E193="",0,E193)-IF(OR(G193="أبو اسحاق",G193="أبو آدم",G193="أبو اسحاق ",G193="أبو آدم "),0,IF(D193="",0,D193)))</f>
-        <v>316.29500000000007</v>
+        <v>318.79500000000007</v>
       </c>
       <c r="K193" s="168"/>
       <c r="L193">
@@ -20566,10 +20566,10 @@
         <v>46276</v>
       </c>
       <c r="B194" s="36" t="s">
+        <v>419</v>
+      </c>
+      <c r="C194" s="37" t="s">
         <v>420</v>
-      </c>
-      <c r="C194" s="37" t="s">
-        <v>421</v>
       </c>
       <c r="D194" s="38"/>
       <c r="E194" s="39">
@@ -20585,7 +20585,7 @@
       <c r="I194" s="42"/>
       <c r="J194" s="43">
         <f>IF(AND(D194="",E194="",A194="",B194="",C194=""),"", IFERROR(IF(J193="",D2,J193),D2)+IF(E194="",0,E194)-IF(OR(G194="أبو اسحاق",G194="أبو آدم",G194="أبو اسحاق ",G194="أبو آدم "),0,IF(D194="",0,D194)))</f>
-        <v>322.29500000000007</v>
+        <v>324.79500000000007</v>
       </c>
       <c r="K194" s="44"/>
       <c r="L194">
@@ -20618,10 +20618,10 @@
         <v>46276</v>
       </c>
       <c r="B195" s="36" t="s">
+        <v>421</v>
+      </c>
+      <c r="C195" s="27" t="s">
         <v>422</v>
-      </c>
-      <c r="C195" s="27" t="s">
-        <v>423</v>
       </c>
       <c r="D195" s="28"/>
       <c r="E195" s="29">
@@ -20637,7 +20637,7 @@
       <c r="I195" s="33"/>
       <c r="J195" s="34">
         <f>IF(AND(D195="",E195="",A195="",B195="",C195=""),"", IFERROR(IF(J194="",D2,J194),D2)+IF(E195="",0,E195)-IF(OR(G195="أبو اسحاق",G195="أبو آدم",G195="أبو اسحاق ",G195="أبو آدم "),0,IF(D195="",0,D195)))</f>
-        <v>324.29500000000007</v>
+        <v>326.79500000000007</v>
       </c>
       <c r="K195" s="35"/>
       <c r="L195">
@@ -20670,10 +20670,10 @@
         <v>46276</v>
       </c>
       <c r="B196" s="36" t="s">
+        <v>423</v>
+      </c>
+      <c r="C196" s="37" t="s">
         <v>424</v>
-      </c>
-      <c r="C196" s="37" t="s">
-        <v>425</v>
       </c>
       <c r="D196" s="38"/>
       <c r="E196" s="39">
@@ -20689,7 +20689,7 @@
       <c r="I196" s="42"/>
       <c r="J196" s="43">
         <f>IF(AND(D196="",E196="",A196="",B196="",C196=""),"", IFERROR(IF(J195="",D2,J195),D2)+IF(E196="",0,E196)-IF(OR(G196="أبو اسحاق",G196="أبو آدم",G196="أبو اسحاق ",G196="أبو آدم "),0,IF(D196="",0,D196)))</f>
-        <v>329.29500000000007</v>
+        <v>331.79500000000007</v>
       </c>
       <c r="K196" s="44"/>
       <c r="L196">
@@ -20722,10 +20722,10 @@
         <v>46276</v>
       </c>
       <c r="B197" s="36" t="s">
+        <v>425</v>
+      </c>
+      <c r="C197" s="27" t="s">
         <v>426</v>
-      </c>
-      <c r="C197" s="27" t="s">
-        <v>427</v>
       </c>
       <c r="D197" s="28"/>
       <c r="E197" s="29">
@@ -20741,7 +20741,7 @@
       <c r="I197" s="33"/>
       <c r="J197" s="34">
         <f>IF(AND(D197="",E197="",A197="",B197="",C197=""),"", IFERROR(IF(J196="",D2,J196),D2)+IF(E197="",0,E197)-IF(OR(G197="أبو اسحاق",G197="أبو آدم",G197="أبو اسحاق ",G197="أبو آدم "),0,IF(D197="",0,D197)))</f>
-        <v>331.29500000000007</v>
+        <v>333.79500000000007</v>
       </c>
       <c r="K197" s="35"/>
       <c r="L197">
@@ -20774,10 +20774,10 @@
         <v>46276</v>
       </c>
       <c r="B198" s="36" t="s">
+        <v>427</v>
+      </c>
+      <c r="C198" s="37" t="s">
         <v>428</v>
-      </c>
-      <c r="C198" s="37" t="s">
-        <v>429</v>
       </c>
       <c r="D198" s="38"/>
       <c r="E198" s="39">
@@ -20793,7 +20793,7 @@
       <c r="I198" s="42"/>
       <c r="J198" s="43">
         <f>IF(AND(D198="",E198="",A198="",B198="",C198=""),"", IFERROR(IF(J197="",D2,J197),D2)+IF(E198="",0,E198)-IF(OR(G198="أبو اسحاق",G198="أبو آدم",G198="أبو اسحاق ",G198="أبو آدم "),0,IF(D198="",0,D198)))</f>
-        <v>334.29500000000007</v>
+        <v>336.79500000000007</v>
       </c>
       <c r="K198" s="44"/>
       <c r="L198">
@@ -20826,10 +20826,10 @@
         <v>46276</v>
       </c>
       <c r="B199" s="36" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C199" s="27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="D199" s="28"/>
       <c r="E199" s="29">
@@ -20845,7 +20845,7 @@
       <c r="I199" s="33"/>
       <c r="J199" s="34">
         <f>IF(AND(D199="",E199="",A199="",B199="",C199=""),"", IFERROR(IF(J198="",D2,J198),D2)+IF(E199="",0,E199)-IF(OR(G199="أبو اسحاق",G199="أبو آدم",G199="أبو اسحاق ",G199="أبو آدم "),0,IF(D199="",0,D199)))</f>
-        <v>336.29500000000007</v>
+        <v>338.79500000000007</v>
       </c>
       <c r="K199" s="35"/>
       <c r="L199">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="B200" s="36"/>
       <c r="C200" s="37" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D200" s="38">
         <v>34.5</v>
@@ -20897,7 +20897,7 @@
       <c r="I200" s="42"/>
       <c r="J200" s="43">
         <f>IF(AND(D200="",E200="",A200="",B200="",C200=""),"", IFERROR(IF(J199="",D2,J199),D2)+IF(E200="",0,E200)-IF(OR(G200="أبو اسحاق",G200="أبو آدم",G200="أبو اسحاق ",G200="أبو آدم "),0,IF(D200="",0,D200)))</f>
-        <v>301.79500000000007</v>
+        <v>304.29500000000007</v>
       </c>
       <c r="K200" s="44"/>
       <c r="L200">
@@ -20930,7 +20930,7 @@
         <v>46278</v>
       </c>
       <c r="B201" s="36" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C201" s="27" t="s">
         <v>399</v>
@@ -20949,7 +20949,7 @@
       <c r="I201" s="33"/>
       <c r="J201" s="34">
         <f>IF(AND(D201="",E201="",A201="",B201="",C201=""),"", IFERROR(IF(J200="",D2,J200),D2)+IF(E201="",0,E201)-IF(OR(G201="أبو اسحاق",G201="أبو آدم",G201="أبو اسحاق ",G201="أبو آدم "),0,IF(D201="",0,D201)))</f>
-        <v>611.79500000000007</v>
+        <v>614.29500000000007</v>
       </c>
       <c r="K201" s="35"/>
       <c r="L201" t="str">
@@ -20983,7 +20983,7 @@
       </c>
       <c r="B202" s="36"/>
       <c r="C202" s="37" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="D202" s="38">
         <v>5</v>
@@ -21001,7 +21001,7 @@
       <c r="I202" s="42"/>
       <c r="J202" s="43">
         <f>IF(AND(D202="",E202="",A202="",B202="",C202=""),"", IFERROR(IF(J201="",D2,J201),D2)+IF(E202="",0,E202)-IF(OR(G202="أبو اسحاق",G202="أبو آدم",G202="أبو اسحاق ",G202="أبو آدم "),0,IF(D202="",0,D202)))</f>
-        <v>606.79500000000007</v>
+        <v>609.29500000000007</v>
       </c>
       <c r="K202" s="44"/>
       <c r="L202">
@@ -21121,7 +21121,7 @@
       </c>
       <c r="E205" s="46">
         <f>SUM(E4:E203)</f>
-        <v>2463.19</v>
+        <v>2465.69</v>
       </c>
       <c r="F205" s="140">
         <f>COUNTIF(H4:H203,"معلق")</f>
@@ -28636,7 +28636,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="178" t="s">
+      <c r="A4" s="177" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="159"/>
@@ -29947,7 +29947,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="178" t="s">
+      <c r="A55" s="177" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="159"/>
@@ -29961,7 +29961,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="177" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="159"/>
@@ -31272,7 +31272,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="177" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="159"/>
@@ -31295,7 +31295,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="179">
+      <c r="E108" s="178">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -31304,17 +31304,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10729DD-E050-48C3-B23C-DE58B206E509}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BFF95B-B4BE-407F-BC5F-D3A7FBE8476E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2648,14 +2648,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -30813,7 +30813,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="180" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32124,7 +32124,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="179" t="s">
+      <c r="A55" s="180" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32138,7 +32138,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="181" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33449,7 +33449,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="181" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33472,7 +33472,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="180">
+      <c r="E108" s="181">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33481,17 +33481,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40BFF95B-B4BE-407F-BC5F-D3A7FBE8476E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10D34BC-6609-457D-8187-6A8E482C9BD6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1048" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="455">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -2648,14 +2648,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -21219,7 +21219,9 @@
         <v>38</v>
       </c>
       <c r="G205" s="31"/>
-      <c r="H205" s="32"/>
+      <c r="H205" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I205" s="33"/>
       <c r="J205" s="34">
         <f>IF(AND(D205="",E205="",A205="",B205="",C205=""),"", IFERROR(IF(J204="",D2,J204),D2)+IF(E205="",0,E205)-IF(OR(G205="أبو اسحاق",G205="أبو آدم",G205="أبو اسحاق ",G205="أبو آدم "),0,IF(D205="",0,D205)))</f>
@@ -21265,9 +21267,13 @@
       <c r="E206" s="39">
         <v>10</v>
       </c>
-      <c r="F206" s="136"/>
+      <c r="F206" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G206" s="40"/>
-      <c r="H206" s="41"/>
+      <c r="H206" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I206" s="42"/>
       <c r="J206" s="43">
         <f>IF(AND(D206="",E206="",A206="",B206="",C206=""),"", IFERROR(IF(J205="",D2,J205),D2)+IF(E206="",0,E206)-IF(OR(G206="أبو اسحاق",G206="أبو آدم",G206="أبو اسحاق ",G206="أبو آدم "),0,IF(D206="",0,D206)))</f>
@@ -21313,9 +21319,13 @@
       <c r="E207" s="29">
         <v>10</v>
       </c>
-      <c r="F207" s="30"/>
+      <c r="F207" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G207" s="31"/>
-      <c r="H207" s="32"/>
+      <c r="H207" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I207" s="33"/>
       <c r="J207" s="34">
         <f>IF(AND(D207="",E207="",A207="",B207="",C207=""),"", IFERROR(IF(J206="",D2,J206),D2)+IF(E207="",0,E207)-IF(OR(G207="أبو اسحاق",G207="أبو آدم",G207="أبو اسحاق ",G207="أبو آدم "),0,IF(D207="",0,D207)))</f>
@@ -21361,9 +21371,13 @@
       <c r="E208" s="39">
         <v>10</v>
       </c>
-      <c r="F208" s="136"/>
+      <c r="F208" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G208" s="40"/>
-      <c r="H208" s="41"/>
+      <c r="H208" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I208" s="42"/>
       <c r="J208" s="43">
         <f>IF(AND(D208="",E208="",A208="",B208="",C208=""),"", IFERROR(IF(J207="",D2,J207),D2)+IF(E208="",0,E208)-IF(OR(G208="أبو اسحاق",G208="أبو آدم",G208="أبو اسحاق ",G208="أبو آدم "),0,IF(D208="",0,D208)))</f>
@@ -21409,9 +21423,13 @@
       <c r="E209" s="29">
         <v>9</v>
       </c>
-      <c r="F209" s="30"/>
+      <c r="F209" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G209" s="31"/>
-      <c r="H209" s="32"/>
+      <c r="H209" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I209" s="33"/>
       <c r="J209" s="34">
         <f>IF(AND(D209="",E209="",A209="",B209="",C209=""),"", IFERROR(IF(J208="",D2,J208),D2)+IF(E209="",0,E209)-IF(OR(G209="أبو اسحاق",G209="أبو آدم",G209="أبو اسحاق ",G209="أبو آدم "),0,IF(D209="",0,D209)))</f>
@@ -21459,9 +21477,13 @@
       <c r="E210" s="39">
         <v>6</v>
       </c>
-      <c r="F210" s="136"/>
+      <c r="F210" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G210" s="40"/>
-      <c r="H210" s="41"/>
+      <c r="H210" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I210" s="42"/>
       <c r="J210" s="43">
         <f>IF(AND(D210="",E210="",A210="",B210="",C210=""),"", IFERROR(IF(J209="",D2,J209),D2)+IF(E210="",0,E210)-IF(OR(G210="أبو اسحاق",G210="أبو آدم",G210="أبو اسحاق ",G210="أبو آدم "),0,IF(D210="",0,D210)))</f>
@@ -21507,9 +21529,13 @@
       <c r="E211" s="29">
         <v>30</v>
       </c>
-      <c r="F211" s="30"/>
+      <c r="F211" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G211" s="31"/>
-      <c r="H211" s="32"/>
+      <c r="H211" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I211" s="33"/>
       <c r="J211" s="34">
         <f>IF(AND(D211="",E211="",A211="",B211="",C211=""),"", IFERROR(IF(J210="",D2,J210),D2)+IF(E211="",0,E211)-IF(OR(G211="أبو اسحاق",G211="أبو آدم",G211="أبو اسحاق ",G211="أبو آدم "),0,IF(D211="",0,D211)))</f>
@@ -21555,9 +21581,13 @@
       <c r="E212" s="39">
         <v>7.5</v>
       </c>
-      <c r="F212" s="136"/>
+      <c r="F212" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G212" s="40"/>
-      <c r="H212" s="41"/>
+      <c r="H212" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I212" s="42"/>
       <c r="J212" s="43">
         <f>IF(AND(D212="",E212="",A212="",B212="",C212=""),"", IFERROR(IF(J211="",D2,J211),D2)+IF(E212="",0,E212)-IF(OR(G212="أبو اسحاق",G212="أبو آدم",G212="أبو اسحاق ",G212="أبو آدم "),0,IF(D212="",0,D212)))</f>
@@ -21603,9 +21633,13 @@
       <c r="E213" s="29">
         <v>3</v>
       </c>
-      <c r="F213" s="30"/>
+      <c r="F213" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G213" s="31"/>
-      <c r="H213" s="32"/>
+      <c r="H213" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I213" s="33"/>
       <c r="J213" s="34">
         <f>IF(AND(D213="",E213="",A213="",B213="",C213=""),"", IFERROR(IF(J212="",D2,J212),D2)+IF(E213="",0,E213)-IF(OR(G213="أبو اسحاق",G213="أبو آدم",G213="أبو اسحاق ",G213="أبو آدم "),0,IF(D213="",0,D213)))</f>
@@ -21651,9 +21685,13 @@
       <c r="E214" s="39">
         <v>7.5</v>
       </c>
-      <c r="F214" s="136"/>
+      <c r="F214" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G214" s="40"/>
-      <c r="H214" s="41"/>
+      <c r="H214" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I214" s="42"/>
       <c r="J214" s="43">
         <f>IF(AND(D214="",E214="",A214="",B214="",C214=""),"", IFERROR(IF(J213="",D2,J213),D2)+IF(E214="",0,E214)-IF(OR(G214="أبو اسحاق",G214="أبو آدم",G214="أبو اسحاق ",G214="أبو آدم "),0,IF(D214="",0,D214)))</f>
@@ -30813,7 +30851,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="179" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32124,7 +32162,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="180" t="s">
+      <c r="A55" s="179" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32138,7 +32176,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="179" t="s">
+      <c r="A56" s="181" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33449,7 +33487,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="179" t="s">
+      <c r="A107" s="181" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33472,7 +33510,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="181">
+      <c r="E108" s="180">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33481,17 +33519,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10D34BC-6609-457D-8187-6A8E482C9BD6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C3D9AB-4873-413D-87CC-3018C98BCAFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2648,14 +2648,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3018,7 +3018,7 @@
       <c r="E2" s="155"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>679.04500000000007</v>
+        <v>678.54500000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7962,7 +7962,7 @@
       </c>
       <c r="D194" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(189,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="E194" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(189,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="F194" s="125">
         <f t="shared" si="5"/>
-        <v>671.54500000000007</v>
+        <v>671.04500000000007</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="F195" s="125">
         <f t="shared" si="5"/>
-        <v>679.04500000000007</v>
+        <v>678.54500000000007</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8267,7 +8267,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>2561.69</v>
+        <v>2561.19</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>679.04500000000007</v>
+        <v>678.54500000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -21631,7 +21631,7 @@
       </c>
       <c r="D213" s="28"/>
       <c r="E213" s="29">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="F213" s="30" t="s">
         <v>38</v>
@@ -21643,7 +21643,7 @@
       <c r="I213" s="33"/>
       <c r="J213" s="34">
         <f>IF(AND(D213="",E213="",A213="",B213="",C213=""),"", IFERROR(IF(J212="",D2,J212),D2)+IF(E213="",0,E213)-IF(OR(G213="أبو اسحاق",G213="أبو آدم",G213="أبو اسحاق ",G213="أبو آدم "),0,IF(D213="",0,D213)))</f>
-        <v>671.54500000000007</v>
+        <v>671.04500000000007</v>
       </c>
       <c r="K213" s="169"/>
       <c r="L213">
@@ -21695,7 +21695,7 @@
       <c r="I214" s="42"/>
       <c r="J214" s="43">
         <f>IF(AND(D214="",E214="",A214="",B214="",C214=""),"", IFERROR(IF(J213="",D2,J213),D2)+IF(E214="",0,E214)-IF(OR(G214="أبو اسحاق",G214="أبو آدم",G214="أبو اسحاق ",G214="أبو آدم "),0,IF(D214="",0,D214)))</f>
-        <v>679.04500000000007</v>
+        <v>678.54500000000007</v>
       </c>
       <c r="K214" s="170"/>
       <c r="L214">
@@ -23335,7 +23335,7 @@
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
-        <v>2561.69</v>
+        <v>2561.19</v>
       </c>
       <c r="F255" s="140">
         <f>COUNTIF(H4:H253,"معلق")</f>
@@ -30851,7 +30851,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="180" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32162,7 +32162,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="179" t="s">
+      <c r="A55" s="180" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32176,7 +32176,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="181" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33487,7 +33487,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="181" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33510,7 +33510,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="180">
+      <c r="E108" s="181">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33519,17 +33519,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01C3D9AB-4873-413D-87CC-3018C98BCAFD}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D588C2-7686-48A4-AC99-D80DC23A3377}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1067" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="468">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1406,7 +1406,46 @@
     <t>زعتر عدد 10 الحبه ,750</t>
   </si>
   <si>
-    <t xml:space="preserve">لم يدفع </t>
+    <t>لم يدفع  63</t>
+  </si>
+  <si>
+    <t>طربال اسود</t>
+  </si>
+  <si>
+    <t>Inv-160</t>
+  </si>
+  <si>
+    <t>التهاني</t>
+  </si>
+  <si>
+    <t>صبار اوليفيرا عدد 25 الحبه 0.750</t>
+  </si>
+  <si>
+    <t>Inv-161</t>
+  </si>
+  <si>
+    <t>متنوع</t>
+  </si>
+  <si>
+    <t>Inv-162</t>
+  </si>
+  <si>
+    <t>Inv-163</t>
+  </si>
+  <si>
+    <t>دارسينا اخضر عدد1 القيمه 2.500</t>
+  </si>
+  <si>
+    <t>Inv-164</t>
+  </si>
+  <si>
+    <t>دارسينا اسودعدد 29 الحبه 2.500</t>
+  </si>
+  <si>
+    <t>Inv-165</t>
+  </si>
+  <si>
+    <t>لم يدفه أبو ادم 79</t>
   </si>
 </sst>
 </file>
@@ -2648,14 +2687,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3018,7 +3057,7 @@
       <c r="E2" s="155"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>678.54500000000007</v>
+        <v>936.79500000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8000,237 +8039,237 @@
       </c>
     </row>
     <row r="196" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="142" t="str">
+      <c r="A196" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(191,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B196" s="122" t="str">
+        <v>46284</v>
+      </c>
+      <c r="B196" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(191,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C196" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(191,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D196" s="123" t="str">
+        <v>طربال اسود</v>
+      </c>
+      <c r="D196" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(191,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E196" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E196" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(191,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F196" s="125" t="str">
+        <v>25</v>
+      </c>
+      <c r="F196" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>653.54500000000007</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="142" t="str">
+      <c r="A197" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(192,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>46284</v>
       </c>
       <c r="B197" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(192,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>Inv-160</v>
       </c>
       <c r="C197" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(192,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D197" s="123" t="str">
+        <v>التهاني</v>
+      </c>
+      <c r="D197" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(192,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E197" s="124" t="str">
+        <v>243</v>
+      </c>
+      <c r="E197" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(192,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F197" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F197" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>896.54500000000007</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="142" t="str">
+      <c r="A198" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(193,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B198" s="122" t="str">
+        <v>46284</v>
+      </c>
+      <c r="B198" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(193,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C198" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(193,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D198" s="123" t="str">
+        <v>صبار اوليفيرا عدد 25 الحبه 0.750</v>
+      </c>
+      <c r="D198" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(193,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E198" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E198" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(193,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F198" s="125" t="str">
+        <v>18.75</v>
+      </c>
+      <c r="F198" s="125">
         <f t="shared" si="5"/>
-        <v/>
+        <v>877.79500000000007</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="142" t="str">
+      <c r="A199" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(194,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="B199" s="122" t="str">
+        <v>46286</v>
+      </c>
+      <c r="B199" s="122">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(194,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>0</v>
       </c>
       <c r="C199" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(194,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D199" s="123" t="str">
+        <v>احواض عدد 1000 مقاس 14 سم</v>
+      </c>
+      <c r="D199" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(194,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E199" s="124" t="str">
+        <v>0</v>
+      </c>
+      <c r="E199" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(194,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F199" s="125" t="str">
+        <v>20</v>
+      </c>
+      <c r="F199" s="125">
         <f t="shared" ref="F199:F205" si="6">IF($A199="","",IF($F198="",0,$F198)+IF($D199="",0,$D199)-IF($E199="",0,$E199))</f>
-        <v/>
+        <v>857.79500000000007</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="142" t="str">
+      <c r="A200" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(195,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>46286</v>
       </c>
       <c r="B200" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(195,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>Inv-161</v>
       </c>
       <c r="C200" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(195,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D200" s="123" t="str">
+        <v>متنوع</v>
+      </c>
+      <c r="D200" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(195,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E200" s="124" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E200" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(195,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F200" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F200" s="125">
         <f t="shared" si="6"/>
-        <v/>
+        <v>859.29500000000007</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="142" t="str">
+      <c r="A201" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(196,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>46286</v>
       </c>
       <c r="B201" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(196,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>Inv-162</v>
       </c>
       <c r="C201" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(196,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D201" s="123" t="str">
+        <v>متنوع</v>
+      </c>
+      <c r="D201" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(196,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E201" s="124" t="str">
+        <v>1</v>
+      </c>
+      <c r="E201" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(196,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F201" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F201" s="125">
         <f t="shared" si="6"/>
-        <v/>
+        <v>860.29500000000007</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="142" t="str">
+      <c r="A202" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(197,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>46286</v>
       </c>
       <c r="B202" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(197,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>Inv-163</v>
       </c>
       <c r="C202" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(197,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D202" s="123" t="str">
+        <v>دارسينا اخضر عدد1 القيمه 2.500</v>
+      </c>
+      <c r="D202" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(197,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E202" s="124" t="str">
+        <v>2.5</v>
+      </c>
+      <c r="E202" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(197,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F202" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F202" s="125">
         <f t="shared" si="6"/>
-        <v/>
+        <v>862.79500000000007</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="142" t="str">
+      <c r="A203" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(198,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>46286</v>
       </c>
       <c r="B203" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(198,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>Inv-164</v>
       </c>
       <c r="C203" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(198,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D203" s="123" t="str">
+        <v>دارسينا اسودعدد 29 الحبه 2.500</v>
+      </c>
+      <c r="D203" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(198,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E203" s="124" t="str">
+        <v>72.5</v>
+      </c>
+      <c r="E203" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(198,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F203" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F203" s="125">
         <f t="shared" si="6"/>
-        <v/>
+        <v>935.29500000000007</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="142" t="str">
+      <c r="A204" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(199,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>46286</v>
       </c>
       <c r="B204" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(199,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>Inv-165</v>
       </c>
       <c r="C204" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(199,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D204" s="123" t="str">
+        <v>متنوع</v>
+      </c>
+      <c r="D204" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(199,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E204" s="124" t="str">
+        <v>1.5</v>
+      </c>
+      <c r="E204" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(199,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F204" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F204" s="125">
         <f t="shared" si="6"/>
-        <v/>
+        <v>936.79500000000007</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8267,15 +8306,15 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>2561.19</v>
+        <v>2883.19</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1882.645</v>
+        <v>1946.395</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>678.54500000000007</v>
+        <v>936.79500000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -21724,18 +21763,30 @@
       </c>
     </row>
     <row r="215" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="25"/>
+      <c r="A215" s="25">
+        <v>46284</v>
+      </c>
       <c r="B215" s="26"/>
-      <c r="C215" s="27"/>
-      <c r="D215" s="28"/>
+      <c r="C215" s="27" t="s">
+        <v>455</v>
+      </c>
+      <c r="D215" s="28">
+        <v>25</v>
+      </c>
       <c r="E215" s="29"/>
-      <c r="F215" s="30"/>
-      <c r="G215" s="31"/>
-      <c r="H215" s="32"/>
+      <c r="F215" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G215" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H215" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I215" s="33"/>
-      <c r="J215" s="34" t="str">
+      <c r="J215" s="34">
         <f>IF(AND(D215="",E215="",A215="",B215="",C215=""),"", IFERROR(IF(J214="",D2,J214),D2)+IF(E215="",0,E215)-IF(OR(G215="أبو اسحاق",G215="أبو آدم",G215="أبو اسحاق ",G215="أبو آدم "),0,IF(D215="",0,D215)))</f>
-        <v/>
+        <v>653.54500000000007</v>
       </c>
       <c r="K215" s="35"/>
       <c r="L215">
@@ -21754,9 +21805,9 @@
         <f>IF(AND(D214&gt;0,F214="أحد الشركاء"),COUNTIFS($D$4:D214,"&gt;"&amp;0,$F$4:F214,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P215" t="str">
+      <c r="P215">
         <f>IF(OR($A215="",$F215="أحد الشركاء",AND($D215="",$E215="")),"",SUMPRODUCT(($A$4:$A215&lt;&gt;"")*($F$4:$F215&lt;&gt;"أحد الشركاء")*((($D$4:$D215&lt;&gt;"")+($E$4:$E215&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>191</v>
       </c>
       <c r="Q215" t="str">
         <f>IF(OR($A215="",$F215&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A215,"&lt;&gt;",$F$4:F215,"أحد الشركاء"))</f>
@@ -21764,27 +21815,39 @@
       </c>
     </row>
     <row r="216" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="25"/>
-      <c r="B216" s="36"/>
-      <c r="C216" s="37"/>
+      <c r="A216" s="25">
+        <v>46284</v>
+      </c>
+      <c r="B216" s="36" t="s">
+        <v>456</v>
+      </c>
+      <c r="C216" s="37" t="s">
+        <v>457</v>
+      </c>
       <c r="D216" s="38"/>
-      <c r="E216" s="39"/>
-      <c r="F216" s="136"/>
+      <c r="E216" s="39">
+        <v>243</v>
+      </c>
+      <c r="F216" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G216" s="40"/>
-      <c r="H216" s="41"/>
+      <c r="H216" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I216" s="42"/>
-      <c r="J216" s="43" t="str">
+      <c r="J216" s="43">
         <f>IF(AND(D216="",E216="",A216="",B216="",C216=""),"", IFERROR(IF(J215="",D2,J215),D2)+IF(E216="",0,E216)-IF(OR(G216="أبو اسحاق",G216="أبو آدم",G216="أبو اسحاق ",G216="أبو آدم "),0,IF(D216="",0,D216)))</f>
-        <v/>
+        <v>896.54500000000007</v>
       </c>
       <c r="K216" s="44"/>
       <c r="L216" t="str">
         <f>IF(E215&gt;0,COUNTIF($E$4:E215,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M216" t="str">
+      <c r="M216">
         <f>IF(AND(D215&gt;0,G215="المحفظة"),COUNTIFS($D$4:D215,"&gt;"&amp;0,$G$4:G215,"المحفظة"),"")</f>
-        <v/>
+        <v>45</v>
       </c>
       <c r="N216" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A216)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A216)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A216&lt;&gt;""),IFERROR(MAX($N$4:N215),0)+1,"")</f>
@@ -21794,9 +21857,9 @@
         <f>IF(AND(D215&gt;0,F215="أحد الشركاء"),COUNTIFS($D$4:D215,"&gt;"&amp;0,$F$4:F215,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P216" t="str">
+      <c r="P216">
         <f>IF(OR($A216="",$F216="أحد الشركاء",AND($D216="",$E216="")),"",SUMPRODUCT(($A$4:$A216&lt;&gt;"")*($F$4:$F216&lt;&gt;"أحد الشركاء")*((($D$4:$D216&lt;&gt;"")+($E$4:$E216&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>192</v>
       </c>
       <c r="Q216" t="str">
         <f>IF(OR($A216="",$F216&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A216,"&lt;&gt;",$F$4:F216,"أحد الشركاء"))</f>
@@ -21804,23 +21867,35 @@
       </c>
     </row>
     <row r="217" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="25"/>
+      <c r="A217" s="25">
+        <v>46284</v>
+      </c>
       <c r="B217" s="26"/>
-      <c r="C217" s="27"/>
-      <c r="D217" s="28"/>
+      <c r="C217" s="27" t="s">
+        <v>458</v>
+      </c>
+      <c r="D217" s="28">
+        <v>18.75</v>
+      </c>
       <c r="E217" s="29"/>
-      <c r="F217" s="30"/>
-      <c r="G217" s="31"/>
-      <c r="H217" s="32"/>
+      <c r="F217" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G217" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H217" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I217" s="33"/>
-      <c r="J217" s="34" t="str">
+      <c r="J217" s="34">
         <f>IF(AND(D217="",E217="",A217="",B217="",C217=""),"", IFERROR(IF(J216="",D2,J216),D2)+IF(E217="",0,E217)-IF(OR(G217="أبو اسحاق",G217="أبو آدم",G217="أبو اسحاق ",G217="أبو آدم "),0,IF(D217="",0,D217)))</f>
-        <v/>
+        <v>877.79500000000007</v>
       </c>
       <c r="K217" s="35"/>
-      <c r="L217" t="str">
+      <c r="L217">
         <f>IF(E216&gt;0,COUNTIF($E$4:E216,"&gt;0"),"")</f>
-        <v/>
+        <v>146</v>
       </c>
       <c r="M217" t="str">
         <f>IF(AND(D216&gt;0,G216="المحفظة"),COUNTIFS($D$4:D216,"&gt;"&amp;0,$G$4:G216,"المحفظة"),"")</f>
@@ -21834,9 +21909,9 @@
         <f>IF(AND(D216&gt;0,F216="أحد الشركاء"),COUNTIFS($D$4:D216,"&gt;"&amp;0,$F$4:F216,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P217" t="str">
+      <c r="P217">
         <f>IF(OR($A217="",$F217="أحد الشركاء",AND($D217="",$E217="")),"",SUMPRODUCT(($A$4:$A217&lt;&gt;"")*($F$4:$F217&lt;&gt;"أحد الشركاء")*((($D$4:$D217&lt;&gt;"")+($E$4:$E217&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>193</v>
       </c>
       <c r="Q217" t="str">
         <f>IF(OR($A217="",$F217&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A217,"&lt;&gt;",$F$4:F217,"أحد الشركاء"))</f>
@@ -21844,27 +21919,39 @@
       </c>
     </row>
     <row r="218" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="25"/>
+      <c r="A218" s="25">
+        <v>46286</v>
+      </c>
       <c r="B218" s="36"/>
-      <c r="C218" s="37"/>
-      <c r="D218" s="38"/>
+      <c r="C218" s="37" t="s">
+        <v>208</v>
+      </c>
+      <c r="D218" s="38">
+        <v>20</v>
+      </c>
       <c r="E218" s="39"/>
-      <c r="F218" s="136"/>
-      <c r="G218" s="40"/>
-      <c r="H218" s="41"/>
+      <c r="F218" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G218" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H218" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I218" s="42"/>
-      <c r="J218" s="43" t="str">
+      <c r="J218" s="43">
         <f>IF(AND(D218="",E218="",A218="",B218="",C218=""),"", IFERROR(IF(J217="",D2,J217),D2)+IF(E218="",0,E218)-IF(OR(G218="أبو اسحاق",G218="أبو آدم",G218="أبو اسحاق ",G218="أبو آدم "),0,IF(D218="",0,D218)))</f>
-        <v/>
+        <v>857.79500000000007</v>
       </c>
       <c r="K218" s="44"/>
       <c r="L218" t="str">
         <f>IF(E217&gt;0,COUNTIF($E$4:E217,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M218" t="str">
+      <c r="M218">
         <f>IF(AND(D217&gt;0,G217="المحفظة"),COUNTIFS($D$4:D217,"&gt;"&amp;0,$G$4:G217,"المحفظة"),"")</f>
-        <v/>
+        <v>46</v>
       </c>
       <c r="N218" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A218)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A218)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A218&lt;&gt;""),IFERROR(MAX($N$4:N217),0)+1,"")</f>
@@ -21874,9 +21961,9 @@
         <f>IF(AND(D217&gt;0,F217="أحد الشركاء"),COUNTIFS($D$4:D217,"&gt;"&amp;0,$F$4:F217,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P218" t="str">
+      <c r="P218">
         <f>IF(OR($A218="",$F218="أحد الشركاء",AND($D218="",$E218="")),"",SUMPRODUCT(($A$4:$A218&lt;&gt;"")*($F$4:$F218&lt;&gt;"أحد الشركاء")*((($D$4:$D218&lt;&gt;"")+($E$4:$E218&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>194</v>
       </c>
       <c r="Q218" t="str">
         <f>IF(OR($A218="",$F218&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A218,"&lt;&gt;",$F$4:F218,"أحد الشركاء"))</f>
@@ -21884,27 +21971,41 @@
       </c>
     </row>
     <row r="219" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="25"/>
-      <c r="B219" s="26"/>
-      <c r="C219" s="27"/>
+      <c r="A219" s="25">
+        <v>46286</v>
+      </c>
+      <c r="B219" s="36" t="s">
+        <v>459</v>
+      </c>
+      <c r="C219" s="27" t="s">
+        <v>460</v>
+      </c>
       <c r="D219" s="28"/>
-      <c r="E219" s="29"/>
-      <c r="F219" s="30"/>
+      <c r="E219" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="F219" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G219" s="31"/>
-      <c r="H219" s="32"/>
+      <c r="H219" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I219" s="33"/>
-      <c r="J219" s="34" t="str">
+      <c r="J219" s="34">
         <f>IF(AND(D219="",E219="",A219="",B219="",C219=""),"", IFERROR(IF(J218="",D2,J218),D2)+IF(E219="",0,E219)-IF(OR(G219="أبو اسحاق",G219="أبو آدم",G219="أبو اسحاق ",G219="أبو آدم "),0,IF(D219="",0,D219)))</f>
-        <v/>
-      </c>
-      <c r="K219" s="35"/>
+        <v>859.29500000000007</v>
+      </c>
+      <c r="K219" s="168" t="s">
+        <v>467</v>
+      </c>
       <c r="L219" t="str">
         <f>IF(E218&gt;0,COUNTIF($E$4:E218,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M219" t="str">
+      <c r="M219">
         <f>IF(AND(D218&gt;0,G218="المحفظة"),COUNTIFS($D$4:D218,"&gt;"&amp;0,$G$4:G218,"المحفظة"),"")</f>
-        <v/>
+        <v>47</v>
       </c>
       <c r="N219" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A219)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A219)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A219&lt;&gt;""),IFERROR(MAX($N$4:N218),0)+1,"")</f>
@@ -21914,9 +22015,9 @@
         <f>IF(AND(D218&gt;0,F218="أحد الشركاء"),COUNTIFS($D$4:D218,"&gt;"&amp;0,$F$4:F218,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P219" t="str">
+      <c r="P219">
         <f>IF(OR($A219="",$F219="أحد الشركاء",AND($D219="",$E219="")),"",SUMPRODUCT(($A$4:$A219&lt;&gt;"")*($F$4:$F219&lt;&gt;"أحد الشركاء")*((($D$4:$D219&lt;&gt;"")+($E$4:$E219&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>195</v>
       </c>
       <c r="Q219" t="str">
         <f>IF(OR($A219="",$F219&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A219,"&lt;&gt;",$F$4:F219,"أحد الشركاء"))</f>
@@ -21924,23 +22025,35 @@
       </c>
     </row>
     <row r="220" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="25"/>
-      <c r="B220" s="36"/>
-      <c r="C220" s="37"/>
+      <c r="A220" s="25">
+        <v>46286</v>
+      </c>
+      <c r="B220" s="36" t="s">
+        <v>461</v>
+      </c>
+      <c r="C220" s="37" t="s">
+        <v>460</v>
+      </c>
       <c r="D220" s="38"/>
-      <c r="E220" s="39"/>
-      <c r="F220" s="136"/>
+      <c r="E220" s="39">
+        <v>1</v>
+      </c>
+      <c r="F220" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G220" s="40"/>
-      <c r="H220" s="41"/>
+      <c r="H220" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I220" s="42"/>
-      <c r="J220" s="43" t="str">
+      <c r="J220" s="43">
         <f>IF(AND(D220="",E220="",A220="",B220="",C220=""),"", IFERROR(IF(J219="",D2,J219),D2)+IF(E220="",0,E220)-IF(OR(G220="أبو اسحاق",G220="أبو آدم",G220="أبو اسحاق ",G220="أبو آدم "),0,IF(D220="",0,D220)))</f>
-        <v/>
-      </c>
-      <c r="K220" s="44"/>
-      <c r="L220" t="str">
+        <v>860.29500000000007</v>
+      </c>
+      <c r="K220" s="169"/>
+      <c r="L220">
         <f>IF(E219&gt;0,COUNTIF($E$4:E219,"&gt;0"),"")</f>
-        <v/>
+        <v>147</v>
       </c>
       <c r="M220" t="str">
         <f>IF(AND(D219&gt;0,G219="المحفظة"),COUNTIFS($D$4:D219,"&gt;"&amp;0,$G$4:G219,"المحفظة"),"")</f>
@@ -21954,9 +22067,9 @@
         <f>IF(AND(D219&gt;0,F219="أحد الشركاء"),COUNTIFS($D$4:D219,"&gt;"&amp;0,$F$4:F219,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P220" t="str">
+      <c r="P220">
         <f>IF(OR($A220="",$F220="أحد الشركاء",AND($D220="",$E220="")),"",SUMPRODUCT(($A$4:$A220&lt;&gt;"")*($F$4:$F220&lt;&gt;"أحد الشركاء")*((($D$4:$D220&lt;&gt;"")+($E$4:$E220&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>196</v>
       </c>
       <c r="Q220" t="str">
         <f>IF(OR($A220="",$F220&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A220,"&lt;&gt;",$F$4:F220,"أحد الشركاء"))</f>
@@ -21964,23 +22077,35 @@
       </c>
     </row>
     <row r="221" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="25"/>
-      <c r="B221" s="26"/>
-      <c r="C221" s="27"/>
+      <c r="A221" s="25">
+        <v>46286</v>
+      </c>
+      <c r="B221" s="36" t="s">
+        <v>462</v>
+      </c>
+      <c r="C221" s="27" t="s">
+        <v>463</v>
+      </c>
       <c r="D221" s="28"/>
-      <c r="E221" s="29"/>
-      <c r="F221" s="30"/>
+      <c r="E221" s="29">
+        <v>2.5</v>
+      </c>
+      <c r="F221" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G221" s="31"/>
-      <c r="H221" s="32"/>
+      <c r="H221" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I221" s="33"/>
-      <c r="J221" s="34" t="str">
+      <c r="J221" s="34">
         <f>IF(AND(D221="",E221="",A221="",B221="",C221=""),"", IFERROR(IF(J220="",D2,J220),D2)+IF(E221="",0,E221)-IF(OR(G221="أبو اسحاق",G221="أبو آدم",G221="أبو اسحاق ",G221="أبو آدم "),0,IF(D221="",0,D221)))</f>
-        <v/>
-      </c>
-      <c r="K221" s="35"/>
-      <c r="L221" t="str">
+        <v>862.79500000000007</v>
+      </c>
+      <c r="K221" s="169"/>
+      <c r="L221">
         <f>IF(E220&gt;0,COUNTIF($E$4:E220,"&gt;0"),"")</f>
-        <v/>
+        <v>148</v>
       </c>
       <c r="M221" t="str">
         <f>IF(AND(D220&gt;0,G220="المحفظة"),COUNTIFS($D$4:D220,"&gt;"&amp;0,$G$4:G220,"المحفظة"),"")</f>
@@ -21994,9 +22119,9 @@
         <f>IF(AND(D220&gt;0,F220="أحد الشركاء"),COUNTIFS($D$4:D220,"&gt;"&amp;0,$F$4:F220,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P221" t="str">
+      <c r="P221">
         <f>IF(OR($A221="",$F221="أحد الشركاء",AND($D221="",$E221="")),"",SUMPRODUCT(($A$4:$A221&lt;&gt;"")*($F$4:$F221&lt;&gt;"أحد الشركاء")*((($D$4:$D221&lt;&gt;"")+($E$4:$E221&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>197</v>
       </c>
       <c r="Q221" t="str">
         <f>IF(OR($A221="",$F221&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A221,"&lt;&gt;",$F$4:F221,"أحد الشركاء"))</f>
@@ -22004,23 +22129,35 @@
       </c>
     </row>
     <row r="222" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="25"/>
-      <c r="B222" s="36"/>
-      <c r="C222" s="37"/>
+      <c r="A222" s="25">
+        <v>46286</v>
+      </c>
+      <c r="B222" s="36" t="s">
+        <v>464</v>
+      </c>
+      <c r="C222" s="37" t="s">
+        <v>465</v>
+      </c>
       <c r="D222" s="38"/>
-      <c r="E222" s="39"/>
-      <c r="F222" s="136"/>
+      <c r="E222" s="39">
+        <v>72.5</v>
+      </c>
+      <c r="F222" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G222" s="40"/>
-      <c r="H222" s="41"/>
+      <c r="H222" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I222" s="42"/>
-      <c r="J222" s="43" t="str">
+      <c r="J222" s="43">
         <f>IF(AND(D222="",E222="",A222="",B222="",C222=""),"", IFERROR(IF(J221="",D2,J221),D2)+IF(E222="",0,E222)-IF(OR(G222="أبو اسحاق",G222="أبو آدم",G222="أبو اسحاق ",G222="أبو آدم "),0,IF(D222="",0,D222)))</f>
-        <v/>
-      </c>
-      <c r="K222" s="44"/>
-      <c r="L222" t="str">
+        <v>935.29500000000007</v>
+      </c>
+      <c r="K222" s="169"/>
+      <c r="L222">
         <f>IF(E221&gt;0,COUNTIF($E$4:E221,"&gt;0"),"")</f>
-        <v/>
+        <v>149</v>
       </c>
       <c r="M222" t="str">
         <f>IF(AND(D221&gt;0,G221="المحفظة"),COUNTIFS($D$4:D221,"&gt;"&amp;0,$G$4:G221,"المحفظة"),"")</f>
@@ -22034,9 +22171,9 @@
         <f>IF(AND(D221&gt;0,F221="أحد الشركاء"),COUNTIFS($D$4:D221,"&gt;"&amp;0,$F$4:F221,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P222" t="str">
+      <c r="P222">
         <f>IF(OR($A222="",$F222="أحد الشركاء",AND($D222="",$E222="")),"",SUMPRODUCT(($A$4:$A222&lt;&gt;"")*($F$4:$F222&lt;&gt;"أحد الشركاء")*((($D$4:$D222&lt;&gt;"")+($E$4:$E222&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>198</v>
       </c>
       <c r="Q222" t="str">
         <f>IF(OR($A222="",$F222&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A222,"&lt;&gt;",$F$4:F222,"أحد الشركاء"))</f>
@@ -22044,23 +22181,35 @@
       </c>
     </row>
     <row r="223" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="25"/>
-      <c r="B223" s="26"/>
-      <c r="C223" s="27"/>
+      <c r="A223" s="25">
+        <v>46286</v>
+      </c>
+      <c r="B223" s="36" t="s">
+        <v>466</v>
+      </c>
+      <c r="C223" s="27" t="s">
+        <v>460</v>
+      </c>
       <c r="D223" s="28"/>
-      <c r="E223" s="29"/>
-      <c r="F223" s="30"/>
+      <c r="E223" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="F223" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G223" s="31"/>
-      <c r="H223" s="32"/>
+      <c r="H223" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I223" s="33"/>
-      <c r="J223" s="34" t="str">
+      <c r="J223" s="34">
         <f>IF(AND(D223="",E223="",A223="",B223="",C223=""),"", IFERROR(IF(J222="",D2,J222),D2)+IF(E223="",0,E223)-IF(OR(G223="أبو اسحاق",G223="أبو آدم",G223="أبو اسحاق ",G223="أبو آدم "),0,IF(D223="",0,D223)))</f>
-        <v/>
-      </c>
-      <c r="K223" s="35"/>
-      <c r="L223" t="str">
+        <v>936.79500000000007</v>
+      </c>
+      <c r="K223" s="170"/>
+      <c r="L223">
         <f>IF(E222&gt;0,COUNTIF($E$4:E222,"&gt;0"),"")</f>
-        <v/>
+        <v>150</v>
       </c>
       <c r="M223" t="str">
         <f>IF(AND(D222&gt;0,G222="المحفظة"),COUNTIFS($D$4:D222,"&gt;"&amp;0,$G$4:G222,"المحفظة"),"")</f>
@@ -22074,9 +22223,9 @@
         <f>IF(AND(D222&gt;0,F222="أحد الشركاء"),COUNTIFS($D$4:D222,"&gt;"&amp;0,$F$4:F222,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P223" t="str">
+      <c r="P223">
         <f>IF(OR($A223="",$F223="أحد الشركاء",AND($D223="",$E223="")),"",SUMPRODUCT(($A$4:$A223&lt;&gt;"")*($F$4:$F223&lt;&gt;"أحد الشركاء")*((($D$4:$D223&lt;&gt;"")+($E$4:$E223&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>199</v>
       </c>
       <c r="Q223" t="str">
         <f>IF(OR($A223="",$F223&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A223,"&lt;&gt;",$F$4:F223,"أحد الشركاء"))</f>
@@ -22084,8 +22233,12 @@
       </c>
     </row>
     <row r="224" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="25"/>
-      <c r="B224" s="36"/>
+      <c r="A224" s="25">
+        <v>46286</v>
+      </c>
+      <c r="B224" s="36" t="s">
+        <v>456</v>
+      </c>
       <c r="C224" s="37"/>
       <c r="D224" s="38"/>
       <c r="E224" s="39"/>
@@ -22093,14 +22246,14 @@
       <c r="G224" s="40"/>
       <c r="H224" s="41"/>
       <c r="I224" s="42"/>
-      <c r="J224" s="43" t="str">
+      <c r="J224" s="43">
         <f>IF(AND(D224="",E224="",A224="",B224="",C224=""),"", IFERROR(IF(J223="",D2,J223),D2)+IF(E224="",0,E224)-IF(OR(G224="أبو اسحاق",G224="أبو آدم",G224="أبو اسحاق ",G224="أبو آدم "),0,IF(D224="",0,D224)))</f>
-        <v/>
+        <v>936.79500000000007</v>
       </c>
       <c r="K224" s="44"/>
-      <c r="L224" t="str">
+      <c r="L224">
         <f>IF(E223&gt;0,COUNTIF($E$4:E223,"&gt;0"),"")</f>
-        <v/>
+        <v>151</v>
       </c>
       <c r="M224" t="str">
         <f>IF(AND(D223&gt;0,G223="المحفظة"),COUNTIFS($D$4:D223,"&gt;"&amp;0,$G$4:G223,"المحفظة"),"")</f>
@@ -23331,11 +23484,11 @@
       <c r="C255" s="137"/>
       <c r="D255" s="46">
         <f>SUM(D4:D253)</f>
-        <v>3664.1450000000004</v>
+        <v>3727.8950000000004</v>
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
-        <v>2561.19</v>
+        <v>2883.19</v>
       </c>
       <c r="F255" s="140">
         <f>COUNTIF(H4:H253,"معلق")</f>
@@ -23367,7 +23520,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="F254:H254"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="E2:K2"/>
@@ -23375,6 +23528,7 @@
     <mergeCell ref="A254:C254"/>
     <mergeCell ref="K189:K193"/>
     <mergeCell ref="K209:K214"/>
+    <mergeCell ref="K219:K223"/>
   </mergeCells>
   <conditionalFormatting sqref="J4:J253">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
@@ -30851,7 +31005,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="179" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32162,7 +32316,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="180" t="s">
+      <c r="A55" s="179" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32176,7 +32330,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="179" t="s">
+      <c r="A56" s="181" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33487,7 +33641,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="179" t="s">
+      <c r="A107" s="181" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33510,7 +33664,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="181">
+      <c r="E108" s="180">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33519,17 +33673,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06D588C2-7686-48A4-AC99-D80DC23A3377}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF843F3-065A-4889-872E-CDD8CD1C7A6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="468">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="480">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1446,6 +1446,42 @@
   </si>
   <si>
     <t>لم يدفه أبو ادم 79</t>
+  </si>
+  <si>
+    <t>Inv-166</t>
+  </si>
+  <si>
+    <t>Inv-167</t>
+  </si>
+  <si>
+    <t>صبار عدد 60 الحبه .750</t>
+  </si>
+  <si>
+    <t>تين عدد 10 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-168</t>
+  </si>
+  <si>
+    <t>Inv-169</t>
+  </si>
+  <si>
+    <t>Inv-170</t>
+  </si>
+  <si>
+    <t>Inv-171</t>
+  </si>
+  <si>
+    <t>Inv-172</t>
+  </si>
+  <si>
+    <t>اناناس عدد6الحبه 4</t>
+  </si>
+  <si>
+    <t>عطره عدد 20 الحبه .650</t>
+  </si>
+  <si>
+    <t>أبو ادم لم يدفع 66</t>
   </si>
 </sst>
 </file>
@@ -2687,14 +2723,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3057,7 +3093,7 @@
       <c r="E2" s="155"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>936.79500000000007</v>
+        <v>981.79500000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -8273,29 +8309,29 @@
       </c>
     </row>
     <row r="205" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="142" t="str">
+      <c r="A205" s="142">
         <f>IFERROR(INDEX('كشف الحساب'!$A$4:$A$254,MATCH(200,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>46287</v>
       </c>
       <c r="B205" s="122" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$B$4:$B$254,MATCH(200,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
+        <v>Inv-166</v>
       </c>
       <c r="C205" s="121" t="str">
         <f>IFERROR(INDEX('كشف الحساب'!$C$4:$C$254,MATCH(200,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="D205" s="123" t="str">
+        <v>صبار عدد 60 الحبه .750</v>
+      </c>
+      <c r="D205" s="123">
         <f>IFERROR(INDEX('كشف الحساب'!$E$4:$E$254,MATCH(200,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="E205" s="124" t="str">
+        <v>45</v>
+      </c>
+      <c r="E205" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(200,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v/>
-      </c>
-      <c r="F205" s="125" t="str">
+        <v>0</v>
+      </c>
+      <c r="F205" s="125">
         <f t="shared" si="6"/>
-        <v/>
+        <v>981.79500000000007</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8306,7 +8342,7 @@
       </c>
       <c r="D206" s="128">
         <f>SUM(D6:D205)</f>
-        <v>2883.19</v>
+        <v>2928.19</v>
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
@@ -8314,7 +8350,7 @@
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>936.79500000000007</v>
+        <v>981.79500000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -22234,21 +22270,29 @@
     </row>
     <row r="224" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="25">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="B224" s="36" t="s">
-        <v>456</v>
-      </c>
-      <c r="C224" s="37"/>
+        <v>468</v>
+      </c>
+      <c r="C224" s="37" t="s">
+        <v>470</v>
+      </c>
       <c r="D224" s="38"/>
-      <c r="E224" s="39"/>
-      <c r="F224" s="136"/>
+      <c r="E224" s="39">
+        <v>45</v>
+      </c>
+      <c r="F224" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G224" s="40"/>
-      <c r="H224" s="41"/>
+      <c r="H224" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I224" s="42"/>
       <c r="J224" s="43">
         <f>IF(AND(D224="",E224="",A224="",B224="",C224=""),"", IFERROR(IF(J223="",D2,J223),D2)+IF(E224="",0,E224)-IF(OR(G224="أبو اسحاق",G224="أبو آدم",G224="أبو اسحاق ",G224="أبو آدم "),0,IF(D224="",0,D224)))</f>
-        <v>936.79500000000007</v>
+        <v>981.79500000000007</v>
       </c>
       <c r="K224" s="44"/>
       <c r="L224">
@@ -22267,9 +22311,9 @@
         <f>IF(AND(D223&gt;0,F223="أحد الشركاء"),COUNTIFS($D$4:D223,"&gt;"&amp;0,$F$4:F223,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P224" t="str">
+      <c r="P224">
         <f>IF(OR($A224="",$F224="أحد الشركاء",AND($D224="",$E224="")),"",SUMPRODUCT(($A$4:$A224&lt;&gt;"")*($F$4:$F224&lt;&gt;"أحد الشركاء")*((($D$4:$D224&lt;&gt;"")+($E$4:$E224&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>200</v>
       </c>
       <c r="Q224" t="str">
         <f>IF(OR($A224="",$F224&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A224,"&lt;&gt;",$F$4:F224,"أحد الشركاء"))</f>
@@ -22277,23 +22321,35 @@
       </c>
     </row>
     <row r="225" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="25"/>
-      <c r="B225" s="26"/>
-      <c r="C225" s="27"/>
+      <c r="A225" s="25">
+        <v>46287</v>
+      </c>
+      <c r="B225" s="26" t="s">
+        <v>469</v>
+      </c>
+      <c r="C225" s="27" t="s">
+        <v>460</v>
+      </c>
       <c r="D225" s="28"/>
-      <c r="E225" s="29"/>
-      <c r="F225" s="30"/>
+      <c r="E225" s="29">
+        <v>5</v>
+      </c>
+      <c r="F225" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G225" s="31"/>
-      <c r="H225" s="32"/>
+      <c r="H225" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I225" s="33"/>
-      <c r="J225" s="34" t="str">
+      <c r="J225" s="34">
         <f>IF(AND(D225="",E225="",A225="",B225="",C225=""),"", IFERROR(IF(J224="",D2,J224),D2)+IF(E225="",0,E225)-IF(OR(G225="أبو اسحاق",G225="أبو آدم",G225="أبو اسحاق ",G225="أبو آدم "),0,IF(D225="",0,D225)))</f>
-        <v/>
+        <v>986.79500000000007</v>
       </c>
       <c r="K225" s="35"/>
-      <c r="L225" t="str">
+      <c r="L225">
         <f>IF(E224&gt;0,COUNTIF($E$4:E224,"&gt;0"),"")</f>
-        <v/>
+        <v>152</v>
       </c>
       <c r="M225" t="str">
         <f>IF(AND(D224&gt;0,G224="المحفظة"),COUNTIFS($D$4:D224,"&gt;"&amp;0,$G$4:G224,"المحفظة"),"")</f>
@@ -22307,9 +22363,9 @@
         <f>IF(AND(D224&gt;0,F224="أحد الشركاء"),COUNTIFS($D$4:D224,"&gt;"&amp;0,$F$4:F224,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P225" t="str">
+      <c r="P225">
         <f>IF(OR($A225="",$F225="أحد الشركاء",AND($D225="",$E225="")),"",SUMPRODUCT(($A$4:$A225&lt;&gt;"")*($F$4:$F225&lt;&gt;"أحد الشركاء")*((($D$4:$D225&lt;&gt;"")+($E$4:$E225&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>201</v>
       </c>
       <c r="Q225" t="str">
         <f>IF(OR($A225="",$F225&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A225,"&lt;&gt;",$F$4:F225,"أحد الشركاء"))</f>
@@ -22317,23 +22373,35 @@
       </c>
     </row>
     <row r="226" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="25"/>
-      <c r="B226" s="36"/>
-      <c r="C226" s="37"/>
+      <c r="A226" s="25">
+        <v>46287</v>
+      </c>
+      <c r="B226" s="36" t="s">
+        <v>472</v>
+      </c>
+      <c r="C226" s="37" t="s">
+        <v>471</v>
+      </c>
       <c r="D226" s="38"/>
-      <c r="E226" s="39"/>
-      <c r="F226" s="136"/>
+      <c r="E226" s="39">
+        <v>10</v>
+      </c>
+      <c r="F226" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G226" s="40"/>
-      <c r="H226" s="41"/>
+      <c r="H226" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I226" s="42"/>
-      <c r="J226" s="43" t="str">
+      <c r="J226" s="43">
         <f>IF(AND(D226="",E226="",A226="",B226="",C226=""),"", IFERROR(IF(J225="",D2,J225),D2)+IF(E226="",0,E226)-IF(OR(G226="أبو اسحاق",G226="أبو آدم",G226="أبو اسحاق ",G226="أبو آدم "),0,IF(D226="",0,D226)))</f>
-        <v/>
+        <v>996.79500000000007</v>
       </c>
       <c r="K226" s="44"/>
-      <c r="L226" t="str">
+      <c r="L226">
         <f>IF(E225&gt;0,COUNTIF($E$4:E225,"&gt;0"),"")</f>
-        <v/>
+        <v>153</v>
       </c>
       <c r="M226" t="str">
         <f>IF(AND(D225&gt;0,G225="المحفظة"),COUNTIFS($D$4:D225,"&gt;"&amp;0,$G$4:G225,"المحفظة"),"")</f>
@@ -22347,9 +22415,9 @@
         <f>IF(AND(D225&gt;0,F225="أحد الشركاء"),COUNTIFS($D$4:D225,"&gt;"&amp;0,$F$4:F225,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P226" t="str">
+      <c r="P226">
         <f>IF(OR($A226="",$F226="أحد الشركاء",AND($D226="",$E226="")),"",SUMPRODUCT(($A$4:$A226&lt;&gt;"")*($F$4:$F226&lt;&gt;"أحد الشركاء")*((($D$4:$D226&lt;&gt;"")+($E$4:$E226&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>202</v>
       </c>
       <c r="Q226" t="str">
         <f>IF(OR($A226="",$F226&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A226,"&lt;&gt;",$F$4:F226,"أحد الشركاء"))</f>
@@ -22357,23 +22425,37 @@
       </c>
     </row>
     <row r="227" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="25"/>
-      <c r="B227" s="26"/>
-      <c r="C227" s="27"/>
+      <c r="A227" s="25">
+        <v>46287</v>
+      </c>
+      <c r="B227" s="26" t="s">
+        <v>473</v>
+      </c>
+      <c r="C227" s="27" t="s">
+        <v>460</v>
+      </c>
       <c r="D227" s="28"/>
-      <c r="E227" s="29"/>
-      <c r="F227" s="30"/>
+      <c r="E227" s="29">
+        <v>20</v>
+      </c>
+      <c r="F227" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G227" s="31"/>
-      <c r="H227" s="32"/>
+      <c r="H227" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I227" s="33"/>
-      <c r="J227" s="34" t="str">
+      <c r="J227" s="34">
         <f>IF(AND(D227="",E227="",A227="",B227="",C227=""),"", IFERROR(IF(J226="",D2,J226),D2)+IF(E227="",0,E227)-IF(OR(G227="أبو اسحاق",G227="أبو آدم",G227="أبو اسحاق ",G227="أبو آدم "),0,IF(D227="",0,D227)))</f>
-        <v/>
-      </c>
-      <c r="K227" s="35"/>
-      <c r="L227" t="str">
+        <v>1016.7950000000001</v>
+      </c>
+      <c r="K227" s="168" t="s">
+        <v>479</v>
+      </c>
+      <c r="L227">
         <f>IF(E226&gt;0,COUNTIF($E$4:E226,"&gt;0"),"")</f>
-        <v/>
+        <v>154</v>
       </c>
       <c r="M227" t="str">
         <f>IF(AND(D226&gt;0,G226="المحفظة"),COUNTIFS($D$4:D226,"&gt;"&amp;0,$G$4:G226,"المحفظة"),"")</f>
@@ -22387,9 +22469,9 @@
         <f>IF(AND(D226&gt;0,F226="أحد الشركاء"),COUNTIFS($D$4:D226,"&gt;"&amp;0,$F$4:F226,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P227" t="str">
+      <c r="P227">
         <f>IF(OR($A227="",$F227="أحد الشركاء",AND($D227="",$E227="")),"",SUMPRODUCT(($A$4:$A227&lt;&gt;"")*($F$4:$F227&lt;&gt;"أحد الشركاء")*((($D$4:$D227&lt;&gt;"")+($E$4:$E227&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>203</v>
       </c>
       <c r="Q227" t="str">
         <f>IF(OR($A227="",$F227&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A227,"&lt;&gt;",$F$4:F227,"أحد الشركاء"))</f>
@@ -22397,23 +22479,35 @@
       </c>
     </row>
     <row r="228" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="25"/>
-      <c r="B228" s="36"/>
-      <c r="C228" s="37"/>
+      <c r="A228" s="25">
+        <v>46287</v>
+      </c>
+      <c r="B228" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="C228" s="37" t="s">
+        <v>460</v>
+      </c>
       <c r="D228" s="38"/>
-      <c r="E228" s="39"/>
-      <c r="F228" s="136"/>
+      <c r="E228" s="39">
+        <v>9</v>
+      </c>
+      <c r="F228" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G228" s="40"/>
-      <c r="H228" s="41"/>
+      <c r="H228" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I228" s="42"/>
-      <c r="J228" s="43" t="str">
+      <c r="J228" s="43">
         <f>IF(AND(D228="",E228="",A228="",B228="",C228=""),"", IFERROR(IF(J227="",D2,J227),D2)+IF(E228="",0,E228)-IF(OR(G228="أبو اسحاق",G228="أبو آدم",G228="أبو اسحاق ",G228="أبو آدم "),0,IF(D228="",0,D228)))</f>
-        <v/>
-      </c>
-      <c r="K228" s="44"/>
-      <c r="L228" t="str">
+        <v>1025.7950000000001</v>
+      </c>
+      <c r="K228" s="169"/>
+      <c r="L228">
         <f>IF(E227&gt;0,COUNTIF($E$4:E227,"&gt;0"),"")</f>
-        <v/>
+        <v>155</v>
       </c>
       <c r="M228" t="str">
         <f>IF(AND(D227&gt;0,G227="المحفظة"),COUNTIFS($D$4:D227,"&gt;"&amp;0,$G$4:G227,"المحفظة"),"")</f>
@@ -22427,9 +22521,9 @@
         <f>IF(AND(D227&gt;0,F227="أحد الشركاء"),COUNTIFS($D$4:D227,"&gt;"&amp;0,$F$4:F227,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P228" t="str">
+      <c r="P228">
         <f>IF(OR($A228="",$F228="أحد الشركاء",AND($D228="",$E228="")),"",SUMPRODUCT(($A$4:$A228&lt;&gt;"")*($F$4:$F228&lt;&gt;"أحد الشركاء")*((($D$4:$D228&lt;&gt;"")+($E$4:$E228&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>204</v>
       </c>
       <c r="Q228" t="str">
         <f>IF(OR($A228="",$F228&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A228,"&lt;&gt;",$F$4:F228,"أحد الشركاء"))</f>
@@ -22437,23 +22531,35 @@
       </c>
     </row>
     <row r="229" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="25"/>
-      <c r="B229" s="26"/>
-      <c r="C229" s="27"/>
+      <c r="A229" s="25">
+        <v>46287</v>
+      </c>
+      <c r="B229" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="C229" s="27" t="s">
+        <v>477</v>
+      </c>
       <c r="D229" s="28"/>
-      <c r="E229" s="29"/>
-      <c r="F229" s="30"/>
+      <c r="E229" s="29">
+        <v>24</v>
+      </c>
+      <c r="F229" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G229" s="31"/>
-      <c r="H229" s="32"/>
+      <c r="H229" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I229" s="33"/>
-      <c r="J229" s="34" t="str">
+      <c r="J229" s="34">
         <f>IF(AND(D229="",E229="",A229="",B229="",C229=""),"", IFERROR(IF(J228="",D2,J228),D2)+IF(E229="",0,E229)-IF(OR(G229="أبو اسحاق",G229="أبو آدم",G229="أبو اسحاق ",G229="أبو آدم "),0,IF(D229="",0,D229)))</f>
-        <v/>
-      </c>
-      <c r="K229" s="35"/>
-      <c r="L229" t="str">
+        <v>1049.7950000000001</v>
+      </c>
+      <c r="K229" s="169"/>
+      <c r="L229">
         <f>IF(E228&gt;0,COUNTIF($E$4:E228,"&gt;0"),"")</f>
-        <v/>
+        <v>156</v>
       </c>
       <c r="M229" t="str">
         <f>IF(AND(D228&gt;0,G228="المحفظة"),COUNTIFS($D$4:D228,"&gt;"&amp;0,$G$4:G228,"المحفظة"),"")</f>
@@ -22467,9 +22573,9 @@
         <f>IF(AND(D228&gt;0,F228="أحد الشركاء"),COUNTIFS($D$4:D228,"&gt;"&amp;0,$F$4:F228,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P229" t="str">
+      <c r="P229">
         <f>IF(OR($A229="",$F229="أحد الشركاء",AND($D229="",$E229="")),"",SUMPRODUCT(($A$4:$A229&lt;&gt;"")*($F$4:$F229&lt;&gt;"أحد الشركاء")*((($D$4:$D229&lt;&gt;"")+($E$4:$E229&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>205</v>
       </c>
       <c r="Q229" t="str">
         <f>IF(OR($A229="",$F229&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A229,"&lt;&gt;",$F$4:F229,"أحد الشركاء"))</f>
@@ -22477,23 +22583,35 @@
       </c>
     </row>
     <row r="230" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="25"/>
-      <c r="B230" s="36"/>
-      <c r="C230" s="37"/>
+      <c r="A230" s="25">
+        <v>46287</v>
+      </c>
+      <c r="B230" s="36" t="s">
+        <v>476</v>
+      </c>
+      <c r="C230" s="37" t="s">
+        <v>478</v>
+      </c>
       <c r="D230" s="38"/>
-      <c r="E230" s="39"/>
-      <c r="F230" s="136"/>
+      <c r="E230" s="39">
+        <v>13</v>
+      </c>
+      <c r="F230" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G230" s="40"/>
-      <c r="H230" s="41"/>
+      <c r="H230" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I230" s="42"/>
-      <c r="J230" s="43" t="str">
+      <c r="J230" s="43">
         <f>IF(AND(D230="",E230="",A230="",B230="",C230=""),"", IFERROR(IF(J229="",D2,J229),D2)+IF(E230="",0,E230)-IF(OR(G230="أبو اسحاق",G230="أبو آدم",G230="أبو اسحاق ",G230="أبو آدم "),0,IF(D230="",0,D230)))</f>
-        <v/>
-      </c>
-      <c r="K230" s="44"/>
-      <c r="L230" t="str">
+        <v>1062.7950000000001</v>
+      </c>
+      <c r="K230" s="170"/>
+      <c r="L230">
         <f>IF(E229&gt;0,COUNTIF($E$4:E229,"&gt;0"),"")</f>
-        <v/>
+        <v>157</v>
       </c>
       <c r="M230" t="str">
         <f>IF(AND(D229&gt;0,G229="المحفظة"),COUNTIFS($D$4:D229,"&gt;"&amp;0,$G$4:G229,"المحفظة"),"")</f>
@@ -22507,9 +22625,9 @@
         <f>IF(AND(D229&gt;0,F229="أحد الشركاء"),COUNTIFS($D$4:D229,"&gt;"&amp;0,$F$4:F229,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P230" t="str">
+      <c r="P230">
         <f>IF(OR($A230="",$F230="أحد الشركاء",AND($D230="",$E230="")),"",SUMPRODUCT(($A$4:$A230&lt;&gt;"")*($F$4:$F230&lt;&gt;"أحد الشركاء")*((($D$4:$D230&lt;&gt;"")+($E$4:$E230&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>206</v>
       </c>
       <c r="Q230" t="str">
         <f>IF(OR($A230="",$F230&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A230,"&lt;&gt;",$F$4:F230,"أحد الشركاء"))</f>
@@ -22531,9 +22649,9 @@
         <v/>
       </c>
       <c r="K231" s="35"/>
-      <c r="L231" t="str">
+      <c r="L231">
         <f>IF(E230&gt;0,COUNTIF($E$4:E230,"&gt;0"),"")</f>
-        <v/>
+        <v>158</v>
       </c>
       <c r="M231" t="str">
         <f>IF(AND(D230&gt;0,G230="المحفظة"),COUNTIFS($D$4:D230,"&gt;"&amp;0,$G$4:G230,"المحفظة"),"")</f>
@@ -23488,7 +23606,7 @@
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
-        <v>2883.19</v>
+        <v>3009.19</v>
       </c>
       <c r="F255" s="140">
         <f>COUNTIF(H4:H253,"معلق")</f>
@@ -23520,7 +23638,7 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="F254:H254"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="E2:K2"/>
@@ -23529,6 +23647,7 @@
     <mergeCell ref="K189:K193"/>
     <mergeCell ref="K209:K214"/>
     <mergeCell ref="K219:K223"/>
+    <mergeCell ref="K227:K230"/>
   </mergeCells>
   <conditionalFormatting sqref="J4:J253">
     <cfRule type="cellIs" dxfId="5" priority="2" operator="lessThan">
@@ -31005,7 +31124,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="180" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32316,7 +32435,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="179" t="s">
+      <c r="A55" s="180" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32330,7 +32449,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="181" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33641,7 +33760,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="181" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33664,7 +33783,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="180">
+      <c r="E108" s="181">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33673,17 +33792,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF843F3-065A-4889-872E-CDD8CD1C7A6A}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BE0100-2089-4646-8CDD-F1448AE1C2F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="480">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="482">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1482,6 +1482,12 @@
   </si>
   <si>
     <t>أبو ادم لم يدفع 66</t>
+  </si>
+  <si>
+    <t>تاير توكتوك تيوب</t>
+  </si>
+  <si>
+    <t xml:space="preserve">نصف فلتر الماء </t>
   </si>
 </sst>
 </file>
@@ -2723,14 +2729,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22635,18 +22641,30 @@
       </c>
     </row>
     <row r="231" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="25"/>
+      <c r="A231" s="25">
+        <v>46288</v>
+      </c>
       <c r="B231" s="26"/>
-      <c r="C231" s="27"/>
-      <c r="D231" s="28"/>
+      <c r="C231" s="27" t="s">
+        <v>480</v>
+      </c>
+      <c r="D231" s="28">
+        <v>3.5</v>
+      </c>
       <c r="E231" s="29"/>
-      <c r="F231" s="30"/>
-      <c r="G231" s="31"/>
-      <c r="H231" s="32"/>
+      <c r="F231" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G231" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H231" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I231" s="33"/>
-      <c r="J231" s="34" t="str">
+      <c r="J231" s="34">
         <f>IF(AND(D231="",E231="",A231="",B231="",C231=""),"", IFERROR(IF(J230="",D2,J230),D2)+IF(E231="",0,E231)-IF(OR(G231="أبو اسحاق",G231="أبو آدم",G231="أبو اسحاق ",G231="أبو آدم "),0,IF(D231="",0,D231)))</f>
-        <v/>
+        <v>1059.2950000000001</v>
       </c>
       <c r="K231" s="35"/>
       <c r="L231">
@@ -22665,9 +22683,9 @@
         <f>IF(AND(D230&gt;0,F230="أحد الشركاء"),COUNTIFS($D$4:D230,"&gt;"&amp;0,$F$4:F230,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P231" t="str">
+      <c r="P231">
         <f>IF(OR($A231="",$F231="أحد الشركاء",AND($D231="",$E231="")),"",SUMPRODUCT(($A$4:$A231&lt;&gt;"")*($F$4:$F231&lt;&gt;"أحد الشركاء")*((($D$4:$D231&lt;&gt;"")+($E$4:$E231&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>207</v>
       </c>
       <c r="Q231" t="str">
         <f>IF(OR($A231="",$F231&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A231,"&lt;&gt;",$F$4:F231,"أحد الشركاء"))</f>
@@ -22675,27 +22693,39 @@
       </c>
     </row>
     <row r="232" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="25"/>
+      <c r="A232" s="25">
+        <v>46288</v>
+      </c>
       <c r="B232" s="36"/>
-      <c r="C232" s="37"/>
-      <c r="D232" s="38"/>
+      <c r="C232" s="37" t="s">
+        <v>481</v>
+      </c>
+      <c r="D232" s="38">
+        <v>31.5</v>
+      </c>
       <c r="E232" s="39"/>
-      <c r="F232" s="136"/>
-      <c r="G232" s="40"/>
-      <c r="H232" s="41"/>
+      <c r="F232" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G232" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H232" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I232" s="42"/>
-      <c r="J232" s="43" t="str">
+      <c r="J232" s="43">
         <f>IF(AND(D232="",E232="",A232="",B232="",C232=""),"", IFERROR(IF(J231="",D2,J231),D2)+IF(E232="",0,E232)-IF(OR(G232="أبو اسحاق",G232="أبو آدم",G232="أبو اسحاق ",G232="أبو آدم "),0,IF(D232="",0,D232)))</f>
-        <v/>
+        <v>1027.7950000000001</v>
       </c>
       <c r="K232" s="44"/>
       <c r="L232" t="str">
         <f>IF(E231&gt;0,COUNTIF($E$4:E231,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M232" t="str">
+      <c r="M232">
         <f>IF(AND(D231&gt;0,G231="المحفظة"),COUNTIFS($D$4:D231,"&gt;"&amp;0,$G$4:G231,"المحفظة"),"")</f>
-        <v/>
+        <v>48</v>
       </c>
       <c r="N232" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A232)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A232)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A232&lt;&gt;""),IFERROR(MAX($N$4:N231),0)+1,"")</f>
@@ -22705,9 +22735,9 @@
         <f>IF(AND(D231&gt;0,F231="أحد الشركاء"),COUNTIFS($D$4:D231,"&gt;"&amp;0,$F$4:F231,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P232" t="str">
+      <c r="P232">
         <f>IF(OR($A232="",$F232="أحد الشركاء",AND($D232="",$E232="")),"",SUMPRODUCT(($A$4:$A232&lt;&gt;"")*($F$4:$F232&lt;&gt;"أحد الشركاء")*((($D$4:$D232&lt;&gt;"")+($E$4:$E232&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>208</v>
       </c>
       <c r="Q232" t="str">
         <f>IF(OR($A232="",$F232&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A232,"&lt;&gt;",$F$4:F232,"أحد الشركاء"))</f>
@@ -22733,9 +22763,9 @@
         <f>IF(E232&gt;0,COUNTIF($E$4:E232,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M233" t="str">
+      <c r="M233">
         <f>IF(AND(D232&gt;0,G232="المحفظة"),COUNTIFS($D$4:D232,"&gt;"&amp;0,$G$4:G232,"المحفظة"),"")</f>
-        <v/>
+        <v>49</v>
       </c>
       <c r="N233" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A233)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A233)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A233&lt;&gt;""),IFERROR(MAX($N$4:N232),0)+1,"")</f>
@@ -23602,7 +23632,7 @@
       <c r="C255" s="137"/>
       <c r="D255" s="46">
         <f>SUM(D4:D253)</f>
-        <v>3727.8950000000004</v>
+        <v>3762.8950000000004</v>
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
@@ -31124,7 +31154,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="179" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32435,7 +32465,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="180" t="s">
+      <c r="A55" s="179" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32449,7 +32479,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="179" t="s">
+      <c r="A56" s="181" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33760,7 +33790,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="179" t="s">
+      <c r="A107" s="181" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33783,7 +33813,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="181">
+      <c r="E108" s="180">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33792,17 +33822,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BE0100-2089-4646-8CDD-F1448AE1C2F0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD545EA-53D3-4B3A-A6B7-8C3E4936A63B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1141" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="498">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1488,6 +1488,54 @@
   </si>
   <si>
     <t xml:space="preserve">نصف فلتر الماء </t>
+  </si>
+  <si>
+    <t>Inv-173</t>
+  </si>
+  <si>
+    <t>ياسمين هندي عدد 10 الحبه 1</t>
+  </si>
+  <si>
+    <t>روزميري عدد 10 الحبه.650</t>
+  </si>
+  <si>
+    <t>معلقه كبيره عدد 20 الحبه 1</t>
+  </si>
+  <si>
+    <t>مجنونه قزميه عدد 15 الحبه 1</t>
+  </si>
+  <si>
+    <t>Inv-174</t>
+  </si>
+  <si>
+    <t>Inv-175</t>
+  </si>
+  <si>
+    <t>Inv-176</t>
+  </si>
+  <si>
+    <t>مجموعه متنوعه زهور التهاني</t>
+  </si>
+  <si>
+    <t>Inv-177</t>
+  </si>
+  <si>
+    <t>عطره معلقه عدد 1 الحبه 1.500</t>
+  </si>
+  <si>
+    <t>دارسينا صغيره عدد 1 الحبه 1.500</t>
+  </si>
+  <si>
+    <t>Inv-178</t>
+  </si>
+  <si>
+    <t>Inv-179</t>
+  </si>
+  <si>
+    <t>متنوع عدد 120 الحبه 1.500</t>
+  </si>
+  <si>
+    <t>Inv-180</t>
   </si>
 </sst>
 </file>
@@ -2729,14 +2777,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -22745,18 +22793,30 @@
       </c>
     </row>
     <row r="233" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="25"/>
-      <c r="B233" s="26"/>
-      <c r="C233" s="27"/>
+      <c r="A233" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B233" s="26" t="s">
+        <v>482</v>
+      </c>
+      <c r="C233" s="27" t="s">
+        <v>483</v>
+      </c>
       <c r="D233" s="28"/>
-      <c r="E233" s="29"/>
-      <c r="F233" s="30"/>
+      <c r="E233" s="29">
+        <v>10</v>
+      </c>
+      <c r="F233" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G233" s="31"/>
-      <c r="H233" s="32"/>
+      <c r="H233" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I233" s="33"/>
-      <c r="J233" s="34" t="str">
+      <c r="J233" s="34">
         <f>IF(AND(D233="",E233="",A233="",B233="",C233=""),"", IFERROR(IF(J232="",D2,J232),D2)+IF(E233="",0,E233)-IF(OR(G233="أبو اسحاق",G233="أبو آدم",G233="أبو اسحاق ",G233="أبو آدم "),0,IF(D233="",0,D233)))</f>
-        <v/>
+        <v>1037.7950000000001</v>
       </c>
       <c r="K233" s="35"/>
       <c r="L233" t="str">
@@ -22775,9 +22835,9 @@
         <f>IF(AND(D232&gt;0,F232="أحد الشركاء"),COUNTIFS($D$4:D232,"&gt;"&amp;0,$F$4:F232,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P233" t="str">
+      <c r="P233">
         <f>IF(OR($A233="",$F233="أحد الشركاء",AND($D233="",$E233="")),"",SUMPRODUCT(($A$4:$A233&lt;&gt;"")*($F$4:$F233&lt;&gt;"أحد الشركاء")*((($D$4:$D233&lt;&gt;"")+($E$4:$E233&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>209</v>
       </c>
       <c r="Q233" t="str">
         <f>IF(OR($A233="",$F233&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A233,"&lt;&gt;",$F$4:F233,"أحد الشركاء"))</f>
@@ -22785,23 +22845,35 @@
       </c>
     </row>
     <row r="234" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="25"/>
-      <c r="B234" s="36"/>
-      <c r="C234" s="37"/>
+      <c r="A234" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B234" s="36" t="s">
+        <v>487</v>
+      </c>
+      <c r="C234" s="37" t="s">
+        <v>484</v>
+      </c>
       <c r="D234" s="38"/>
-      <c r="E234" s="39"/>
-      <c r="F234" s="136"/>
+      <c r="E234" s="39">
+        <v>9.75</v>
+      </c>
+      <c r="F234" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G234" s="40"/>
-      <c r="H234" s="41"/>
+      <c r="H234" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I234" s="42"/>
-      <c r="J234" s="43" t="str">
+      <c r="J234" s="43">
         <f>IF(AND(D234="",E234="",A234="",B234="",C234=""),"", IFERROR(IF(J233="",D2,J233),D2)+IF(E234="",0,E234)-IF(OR(G234="أبو اسحاق",G234="أبو آدم",G234="أبو اسحاق ",G234="أبو آدم "),0,IF(D234="",0,D234)))</f>
-        <v/>
+        <v>1047.5450000000001</v>
       </c>
       <c r="K234" s="44"/>
-      <c r="L234" t="str">
+      <c r="L234">
         <f>IF(E233&gt;0,COUNTIF($E$4:E233,"&gt;0"),"")</f>
-        <v/>
+        <v>159</v>
       </c>
       <c r="M234" t="str">
         <f>IF(AND(D233&gt;0,G233="المحفظة"),COUNTIFS($D$4:D233,"&gt;"&amp;0,$G$4:G233,"المحفظة"),"")</f>
@@ -22815,9 +22887,9 @@
         <f>IF(AND(D233&gt;0,F233="أحد الشركاء"),COUNTIFS($D$4:D233,"&gt;"&amp;0,$F$4:F233,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P234" t="str">
+      <c r="P234">
         <f>IF(OR($A234="",$F234="أحد الشركاء",AND($D234="",$E234="")),"",SUMPRODUCT(($A$4:$A234&lt;&gt;"")*($F$4:$F234&lt;&gt;"أحد الشركاء")*((($D$4:$D234&lt;&gt;"")+($E$4:$E234&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>210</v>
       </c>
       <c r="Q234" t="str">
         <f>IF(OR($A234="",$F234&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A234,"&lt;&gt;",$F$4:F234,"أحد الشركاء"))</f>
@@ -22825,23 +22897,35 @@
       </c>
     </row>
     <row r="235" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="25"/>
-      <c r="B235" s="26"/>
-      <c r="C235" s="27"/>
+      <c r="A235" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B235" s="26" t="s">
+        <v>488</v>
+      </c>
+      <c r="C235" s="27" t="s">
+        <v>485</v>
+      </c>
       <c r="D235" s="28"/>
-      <c r="E235" s="29"/>
-      <c r="F235" s="30"/>
+      <c r="E235" s="29">
+        <v>20</v>
+      </c>
+      <c r="F235" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G235" s="31"/>
-      <c r="H235" s="32"/>
+      <c r="H235" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I235" s="33"/>
-      <c r="J235" s="34" t="str">
+      <c r="J235" s="34">
         <f>IF(AND(D235="",E235="",A235="",B235="",C235=""),"", IFERROR(IF(J234="",D2,J234),D2)+IF(E235="",0,E235)-IF(OR(G235="أبو اسحاق",G235="أبو آدم",G235="أبو اسحاق ",G235="أبو آدم "),0,IF(D235="",0,D235)))</f>
-        <v/>
+        <v>1067.5450000000001</v>
       </c>
       <c r="K235" s="35"/>
-      <c r="L235" t="str">
+      <c r="L235">
         <f>IF(E234&gt;0,COUNTIF($E$4:E234,"&gt;0"),"")</f>
-        <v/>
+        <v>160</v>
       </c>
       <c r="M235" t="str">
         <f>IF(AND(D234&gt;0,G234="المحفظة"),COUNTIFS($D$4:D234,"&gt;"&amp;0,$G$4:G234,"المحفظة"),"")</f>
@@ -22855,9 +22939,9 @@
         <f>IF(AND(D234&gt;0,F234="أحد الشركاء"),COUNTIFS($D$4:D234,"&gt;"&amp;0,$F$4:F234,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P235" t="str">
+      <c r="P235">
         <f>IF(OR($A235="",$F235="أحد الشركاء",AND($D235="",$E235="")),"",SUMPRODUCT(($A$4:$A235&lt;&gt;"")*($F$4:$F235&lt;&gt;"أحد الشركاء")*((($D$4:$D235&lt;&gt;"")+($E$4:$E235&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>211</v>
       </c>
       <c r="Q235" t="str">
         <f>IF(OR($A235="",$F235&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A235,"&lt;&gt;",$F$4:F235,"أحد الشركاء"))</f>
@@ -22865,23 +22949,35 @@
       </c>
     </row>
     <row r="236" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="25"/>
-      <c r="B236" s="36"/>
-      <c r="C236" s="37"/>
+      <c r="A236" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B236" s="36" t="s">
+        <v>489</v>
+      </c>
+      <c r="C236" s="37" t="s">
+        <v>486</v>
+      </c>
       <c r="D236" s="38"/>
-      <c r="E236" s="39"/>
-      <c r="F236" s="136"/>
+      <c r="E236" s="39">
+        <v>15</v>
+      </c>
+      <c r="F236" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G236" s="40"/>
-      <c r="H236" s="41"/>
+      <c r="H236" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I236" s="42"/>
-      <c r="J236" s="43" t="str">
+      <c r="J236" s="43">
         <f>IF(AND(D236="",E236="",A236="",B236="",C236=""),"", IFERROR(IF(J235="",D2,J235),D2)+IF(E236="",0,E236)-IF(OR(G236="أبو اسحاق",G236="أبو آدم",G236="أبو اسحاق ",G236="أبو آدم "),0,IF(D236="",0,D236)))</f>
-        <v/>
+        <v>1082.5450000000001</v>
       </c>
       <c r="K236" s="44"/>
-      <c r="L236" t="str">
+      <c r="L236">
         <f>IF(E235&gt;0,COUNTIF($E$4:E235,"&gt;0"),"")</f>
-        <v/>
+        <v>161</v>
       </c>
       <c r="M236" t="str">
         <f>IF(AND(D235&gt;0,G235="المحفظة"),COUNTIFS($D$4:D235,"&gt;"&amp;0,$G$4:G235,"المحفظة"),"")</f>
@@ -22895,9 +22991,9 @@
         <f>IF(AND(D235&gt;0,F235="أحد الشركاء"),COUNTIFS($D$4:D235,"&gt;"&amp;0,$F$4:F235,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P236" t="str">
+      <c r="P236">
         <f>IF(OR($A236="",$F236="أحد الشركاء",AND($D236="",$E236="")),"",SUMPRODUCT(($A$4:$A236&lt;&gt;"")*($F$4:$F236&lt;&gt;"أحد الشركاء")*((($D$4:$D236&lt;&gt;"")+($E$4:$E236&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>212</v>
       </c>
       <c r="Q236" t="str">
         <f>IF(OR($A236="",$F236&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A236,"&lt;&gt;",$F$4:F236,"أحد الشركاء"))</f>
@@ -22905,23 +23001,35 @@
       </c>
     </row>
     <row r="237" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="25"/>
-      <c r="B237" s="26"/>
-      <c r="C237" s="27"/>
+      <c r="A237" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B237" s="26" t="s">
+        <v>491</v>
+      </c>
+      <c r="C237" s="27" t="s">
+        <v>490</v>
+      </c>
       <c r="D237" s="28"/>
-      <c r="E237" s="29"/>
-      <c r="F237" s="30"/>
+      <c r="E237" s="29">
+        <v>260</v>
+      </c>
+      <c r="F237" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G237" s="31"/>
-      <c r="H237" s="32"/>
+      <c r="H237" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I237" s="33"/>
-      <c r="J237" s="34" t="str">
+      <c r="J237" s="34">
         <f>IF(AND(D237="",E237="",A237="",B237="",C237=""),"", IFERROR(IF(J236="",D2,J236),D2)+IF(E237="",0,E237)-IF(OR(G237="أبو اسحاق",G237="أبو آدم",G237="أبو اسحاق ",G237="أبو آدم "),0,IF(D237="",0,D237)))</f>
-        <v/>
+        <v>1342.5450000000001</v>
       </c>
       <c r="K237" s="35"/>
-      <c r="L237" t="str">
+      <c r="L237">
         <f>IF(E236&gt;0,COUNTIF($E$4:E236,"&gt;0"),"")</f>
-        <v/>
+        <v>162</v>
       </c>
       <c r="M237" t="str">
         <f>IF(AND(D236&gt;0,G236="المحفظة"),COUNTIFS($D$4:D236,"&gt;"&amp;0,$G$4:G236,"المحفظة"),"")</f>
@@ -22935,9 +23043,9 @@
         <f>IF(AND(D236&gt;0,F236="أحد الشركاء"),COUNTIFS($D$4:D236,"&gt;"&amp;0,$F$4:F236,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P237" t="str">
+      <c r="P237">
         <f>IF(OR($A237="",$F237="أحد الشركاء",AND($D237="",$E237="")),"",SUMPRODUCT(($A$4:$A237&lt;&gt;"")*($F$4:$F237&lt;&gt;"أحد الشركاء")*((($D$4:$D237&lt;&gt;"")+($E$4:$E237&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>213</v>
       </c>
       <c r="Q237" t="str">
         <f>IF(OR($A237="",$F237&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A237,"&lt;&gt;",$F$4:F237,"أحد الشركاء"))</f>
@@ -22945,23 +23053,35 @@
       </c>
     </row>
     <row r="238" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="25"/>
-      <c r="B238" s="36"/>
-      <c r="C238" s="37"/>
+      <c r="A238" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B238" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="C238" s="37" t="s">
+        <v>492</v>
+      </c>
       <c r="D238" s="38"/>
-      <c r="E238" s="39"/>
-      <c r="F238" s="136"/>
+      <c r="E238" s="39">
+        <v>1.5</v>
+      </c>
+      <c r="F238" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G238" s="40"/>
-      <c r="H238" s="41"/>
+      <c r="H238" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I238" s="42"/>
-      <c r="J238" s="43" t="str">
+      <c r="J238" s="43">
         <f>IF(AND(D238="",E238="",A238="",B238="",C238=""),"", IFERROR(IF(J237="",D2,J237),D2)+IF(E238="",0,E238)-IF(OR(G238="أبو اسحاق",G238="أبو آدم",G238="أبو اسحاق ",G238="أبو آدم "),0,IF(D238="",0,D238)))</f>
-        <v/>
+        <v>1344.0450000000001</v>
       </c>
       <c r="K238" s="44"/>
-      <c r="L238" t="str">
+      <c r="L238">
         <f>IF(E237&gt;0,COUNTIF($E$4:E237,"&gt;0"),"")</f>
-        <v/>
+        <v>163</v>
       </c>
       <c r="M238" t="str">
         <f>IF(AND(D237&gt;0,G237="المحفظة"),COUNTIFS($D$4:D237,"&gt;"&amp;0,$G$4:G237,"المحفظة"),"")</f>
@@ -22975,9 +23095,9 @@
         <f>IF(AND(D237&gt;0,F237="أحد الشركاء"),COUNTIFS($D$4:D237,"&gt;"&amp;0,$F$4:F237,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P238" t="str">
+      <c r="P238">
         <f>IF(OR($A238="",$F238="أحد الشركاء",AND($D238="",$E238="")),"",SUMPRODUCT(($A$4:$A238&lt;&gt;"")*($F$4:$F238&lt;&gt;"أحد الشركاء")*((($D$4:$D238&lt;&gt;"")+($E$4:$E238&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>214</v>
       </c>
       <c r="Q238" t="str">
         <f>IF(OR($A238="",$F238&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A238,"&lt;&gt;",$F$4:F238,"أحد الشركاء"))</f>
@@ -22985,23 +23105,35 @@
       </c>
     </row>
     <row r="239" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="25"/>
-      <c r="B239" s="26"/>
-      <c r="C239" s="27"/>
+      <c r="A239" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B239" s="26" t="s">
+        <v>495</v>
+      </c>
+      <c r="C239" s="27" t="s">
+        <v>493</v>
+      </c>
       <c r="D239" s="28"/>
-      <c r="E239" s="29"/>
-      <c r="F239" s="30"/>
+      <c r="E239" s="29">
+        <v>1.5</v>
+      </c>
+      <c r="F239" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G239" s="31"/>
-      <c r="H239" s="32"/>
+      <c r="H239" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I239" s="33"/>
-      <c r="J239" s="34" t="str">
+      <c r="J239" s="34">
         <f>IF(AND(D239="",E239="",A239="",B239="",C239=""),"", IFERROR(IF(J238="",D2,J238),D2)+IF(E239="",0,E239)-IF(OR(G239="أبو اسحاق",G239="أبو آدم",G239="أبو اسحاق ",G239="أبو آدم "),0,IF(D239="",0,D239)))</f>
-        <v/>
+        <v>1345.5450000000001</v>
       </c>
       <c r="K239" s="35"/>
-      <c r="L239" t="str">
+      <c r="L239">
         <f>IF(E238&gt;0,COUNTIF($E$4:E238,"&gt;0"),"")</f>
-        <v/>
+        <v>164</v>
       </c>
       <c r="M239" t="str">
         <f>IF(AND(D238&gt;0,G238="المحفظة"),COUNTIFS($D$4:D238,"&gt;"&amp;0,$G$4:G238,"المحفظة"),"")</f>
@@ -23015,9 +23147,9 @@
         <f>IF(AND(D238&gt;0,F238="أحد الشركاء"),COUNTIFS($D$4:D238,"&gt;"&amp;0,$F$4:F238,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P239" t="str">
+      <c r="P239">
         <f>IF(OR($A239="",$F239="أحد الشركاء",AND($D239="",$E239="")),"",SUMPRODUCT(($A$4:$A239&lt;&gt;"")*($F$4:$F239&lt;&gt;"أحد الشركاء")*((($D$4:$D239&lt;&gt;"")+($E$4:$E239&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>215</v>
       </c>
       <c r="Q239" t="str">
         <f>IF(OR($A239="",$F239&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A239,"&lt;&gt;",$F$4:F239,"أحد الشركاء"))</f>
@@ -23025,23 +23157,35 @@
       </c>
     </row>
     <row r="240" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="25"/>
-      <c r="B240" s="36"/>
-      <c r="C240" s="37"/>
+      <c r="A240" s="25">
+        <v>46290</v>
+      </c>
+      <c r="B240" s="36" t="s">
+        <v>497</v>
+      </c>
+      <c r="C240" s="37" t="s">
+        <v>496</v>
+      </c>
       <c r="D240" s="38"/>
-      <c r="E240" s="39"/>
-      <c r="F240" s="136"/>
+      <c r="E240" s="39">
+        <v>180</v>
+      </c>
+      <c r="F240" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G240" s="40"/>
-      <c r="H240" s="41"/>
+      <c r="H240" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I240" s="42"/>
-      <c r="J240" s="43" t="str">
+      <c r="J240" s="43">
         <f>IF(AND(D240="",E240="",A240="",B240="",C240=""),"", IFERROR(IF(J239="",D2,J239),D2)+IF(E240="",0,E240)-IF(OR(G240="أبو اسحاق",G240="أبو آدم",G240="أبو اسحاق ",G240="أبو آدم "),0,IF(D240="",0,D240)))</f>
-        <v/>
+        <v>1525.5450000000001</v>
       </c>
       <c r="K240" s="44"/>
-      <c r="L240" t="str">
+      <c r="L240">
         <f>IF(E239&gt;0,COUNTIF($E$4:E239,"&gt;0"),"")</f>
-        <v/>
+        <v>165</v>
       </c>
       <c r="M240" t="str">
         <f>IF(AND(D239&gt;0,G239="المحفظة"),COUNTIFS($D$4:D239,"&gt;"&amp;0,$G$4:G239,"المحفظة"),"")</f>
@@ -23055,9 +23199,9 @@
         <f>IF(AND(D239&gt;0,F239="أحد الشركاء"),COUNTIFS($D$4:D239,"&gt;"&amp;0,$F$4:F239,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P240" t="str">
+      <c r="P240">
         <f>IF(OR($A240="",$F240="أحد الشركاء",AND($D240="",$E240="")),"",SUMPRODUCT(($A$4:$A240&lt;&gt;"")*($F$4:$F240&lt;&gt;"أحد الشركاء")*((($D$4:$D240&lt;&gt;"")+($E$4:$E240&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>216</v>
       </c>
       <c r="Q240" t="str">
         <f>IF(OR($A240="",$F240&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A240,"&lt;&gt;",$F$4:F240,"أحد الشركاء"))</f>
@@ -23079,9 +23223,9 @@
         <v/>
       </c>
       <c r="K241" s="35"/>
-      <c r="L241" t="str">
+      <c r="L241">
         <f>IF(E240&gt;0,COUNTIF($E$4:E240,"&gt;0"),"")</f>
-        <v/>
+        <v>166</v>
       </c>
       <c r="M241" t="str">
         <f>IF(AND(D240&gt;0,G240="المحفظة"),COUNTIFS($D$4:D240,"&gt;"&amp;0,$G$4:G240,"المحفظة"),"")</f>
@@ -23636,7 +23780,7 @@
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
-        <v>3009.19</v>
+        <v>3506.94</v>
       </c>
       <c r="F255" s="140">
         <f>COUNTIF(H4:H253,"معلق")</f>
@@ -31154,7 +31298,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="180" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32465,7 +32609,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="179" t="s">
+      <c r="A55" s="180" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32479,7 +32623,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="181" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33790,7 +33934,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="181" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33813,7 +33957,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="180">
+      <c r="E108" s="181">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33822,17 +33966,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD545EA-53D3-4B3A-A6B7-8C3E4936A63B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C9695F-4C35-4449-980D-EC7DBFDC6107}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1173" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="499">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1536,6 +1536,9 @@
   </si>
   <si>
     <t>Inv-180</t>
+  </si>
+  <si>
+    <t>ياسمين ازرق عدد 5 الحبه 1.250</t>
   </si>
 </sst>
 </file>
@@ -2777,14 +2780,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23209,18 +23212,28 @@
       </c>
     </row>
     <row r="241" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="25"/>
+      <c r="A241" s="25">
+        <v>46292</v>
+      </c>
       <c r="B241" s="26"/>
-      <c r="C241" s="27"/>
-      <c r="D241" s="28"/>
+      <c r="C241" s="27" t="s">
+        <v>498</v>
+      </c>
+      <c r="D241" s="28">
+        <v>6</v>
+      </c>
       <c r="E241" s="29"/>
-      <c r="F241" s="30"/>
+      <c r="F241" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G241" s="31"/>
-      <c r="H241" s="32"/>
+      <c r="H241" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I241" s="33"/>
-      <c r="J241" s="34" t="str">
+      <c r="J241" s="34">
         <f>IF(AND(D241="",E241="",A241="",B241="",C241=""),"", IFERROR(IF(J240="",D2,J240),D2)+IF(E241="",0,E241)-IF(OR(G241="أبو اسحاق",G241="أبو آدم",G241="أبو اسحاق ",G241="أبو آدم "),0,IF(D241="",0,D241)))</f>
-        <v/>
+        <v>1519.5450000000001</v>
       </c>
       <c r="K241" s="35"/>
       <c r="L241">
@@ -23239,9 +23252,9 @@
         <f>IF(AND(D240&gt;0,F240="أحد الشركاء"),COUNTIFS($D$4:D240,"&gt;"&amp;0,$F$4:F240,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P241" t="str">
+      <c r="P241">
         <f>IF(OR($A241="",$F241="أحد الشركاء",AND($D241="",$E241="")),"",SUMPRODUCT(($A$4:$A241&lt;&gt;"")*($F$4:$F241&lt;&gt;"أحد الشركاء")*((($D$4:$D241&lt;&gt;"")+($E$4:$E241&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>217</v>
       </c>
       <c r="Q241" t="str">
         <f>IF(OR($A241="",$F241&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A241,"&lt;&gt;",$F$4:F241,"أحد الشركاء"))</f>
@@ -23776,7 +23789,7 @@
       <c r="C255" s="137"/>
       <c r="D255" s="46">
         <f>SUM(D4:D253)</f>
-        <v>3762.8950000000004</v>
+        <v>3768.8950000000004</v>
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
@@ -31298,7 +31311,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="179" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32609,7 +32622,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="180" t="s">
+      <c r="A55" s="179" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32623,7 +32636,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="179" t="s">
+      <c r="A56" s="181" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33934,7 +33947,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="179" t="s">
+      <c r="A107" s="181" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33957,7 +33970,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="181">
+      <c r="E108" s="180">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33966,17 +33979,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2C9695F-4C35-4449-980D-EC7DBFDC6107}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8992895-B9D0-46C4-BA0E-FA5DCD20E51D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1176" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="503">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1406,9 +1406,6 @@
     <t>زعتر عدد 10 الحبه ,750</t>
   </si>
   <si>
-    <t>لم يدفع  63</t>
-  </si>
-  <si>
     <t>طربال اسود</t>
   </si>
   <si>
@@ -1445,9 +1442,6 @@
     <t>Inv-165</t>
   </si>
   <si>
-    <t>لم يدفه أبو ادم 79</t>
-  </si>
-  <si>
     <t>Inv-166</t>
   </si>
   <si>
@@ -1539,6 +1533,24 @@
   </si>
   <si>
     <t>ياسمين ازرق عدد 5 الحبه 1.250</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> أبو ادم 79 تم دفع 78 خصم دينار</t>
+  </si>
+  <si>
+    <t>تم يدفع  63</t>
+  </si>
+  <si>
+    <t>Inv-181</t>
+  </si>
+  <si>
+    <t>صبار تايجر</t>
+  </si>
+  <si>
+    <t>رمل سافي</t>
+  </si>
+  <si>
+    <t>احواض عدد 3000 الحبه 20 فلس</t>
   </si>
 </sst>
 </file>
@@ -2780,14 +2792,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -21568,7 +21580,7 @@
         <v>625.04500000000007</v>
       </c>
       <c r="K209" s="168" t="s">
-        <v>454</v>
+        <v>498</v>
       </c>
       <c r="L209">
         <f>IF(E208&gt;0,COUNTIF($E$4:E208,"&gt;0"),"")</f>
@@ -21861,7 +21873,7 @@
       </c>
       <c r="B215" s="26"/>
       <c r="C215" s="27" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D215" s="28">
         <v>25</v>
@@ -21912,10 +21924,10 @@
         <v>46284</v>
       </c>
       <c r="B216" s="36" t="s">
+        <v>455</v>
+      </c>
+      <c r="C216" s="37" t="s">
         <v>456</v>
-      </c>
-      <c r="C216" s="37" t="s">
-        <v>457</v>
       </c>
       <c r="D216" s="38"/>
       <c r="E216" s="39">
@@ -21965,7 +21977,7 @@
       </c>
       <c r="B217" s="26"/>
       <c r="C217" s="27" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D217" s="28">
         <v>18.75</v>
@@ -22068,10 +22080,10 @@
         <v>46286</v>
       </c>
       <c r="B219" s="36" t="s">
+        <v>458</v>
+      </c>
+      <c r="C219" s="27" t="s">
         <v>459</v>
-      </c>
-      <c r="C219" s="27" t="s">
-        <v>460</v>
       </c>
       <c r="D219" s="28"/>
       <c r="E219" s="29">
@@ -22090,7 +22102,7 @@
         <v>859.29500000000007</v>
       </c>
       <c r="K219" s="168" t="s">
-        <v>467</v>
+        <v>497</v>
       </c>
       <c r="L219" t="str">
         <f>IF(E218&gt;0,COUNTIF($E$4:E218,"&gt;0"),"")</f>
@@ -22122,10 +22134,10 @@
         <v>46286</v>
       </c>
       <c r="B220" s="36" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C220" s="37" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D220" s="38"/>
       <c r="E220" s="39">
@@ -22174,10 +22186,10 @@
         <v>46286</v>
       </c>
       <c r="B221" s="36" t="s">
+        <v>461</v>
+      </c>
+      <c r="C221" s="27" t="s">
         <v>462</v>
-      </c>
-      <c r="C221" s="27" t="s">
-        <v>463</v>
       </c>
       <c r="D221" s="28"/>
       <c r="E221" s="29">
@@ -22226,10 +22238,10 @@
         <v>46286</v>
       </c>
       <c r="B222" s="36" t="s">
+        <v>463</v>
+      </c>
+      <c r="C222" s="37" t="s">
         <v>464</v>
-      </c>
-      <c r="C222" s="37" t="s">
-        <v>465</v>
       </c>
       <c r="D222" s="38"/>
       <c r="E222" s="39">
@@ -22278,10 +22290,10 @@
         <v>46286</v>
       </c>
       <c r="B223" s="36" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="C223" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D223" s="28"/>
       <c r="E223" s="29">
@@ -22330,10 +22342,10 @@
         <v>46287</v>
       </c>
       <c r="B224" s="36" t="s">
+        <v>466</v>
+      </c>
+      <c r="C224" s="37" t="s">
         <v>468</v>
-      </c>
-      <c r="C224" s="37" t="s">
-        <v>470</v>
       </c>
       <c r="D224" s="38"/>
       <c r="E224" s="39">
@@ -22382,10 +22394,10 @@
         <v>46287</v>
       </c>
       <c r="B225" s="26" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="C225" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D225" s="28"/>
       <c r="E225" s="29">
@@ -22434,10 +22446,10 @@
         <v>46287</v>
       </c>
       <c r="B226" s="36" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="C226" s="37" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="D226" s="38"/>
       <c r="E226" s="39">
@@ -22486,10 +22498,10 @@
         <v>46287</v>
       </c>
       <c r="B227" s="26" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="C227" s="27" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D227" s="28"/>
       <c r="E227" s="29">
@@ -22508,7 +22520,7 @@
         <v>1016.7950000000001</v>
       </c>
       <c r="K227" s="168" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="L227">
         <f>IF(E226&gt;0,COUNTIF($E$4:E226,"&gt;0"),"")</f>
@@ -22540,10 +22552,10 @@
         <v>46287</v>
       </c>
       <c r="B228" s="36" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="C228" s="37" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D228" s="38"/>
       <c r="E228" s="39">
@@ -22592,10 +22604,10 @@
         <v>46287</v>
       </c>
       <c r="B229" s="26" t="s">
+        <v>473</v>
+      </c>
+      <c r="C229" s="27" t="s">
         <v>475</v>
-      </c>
-      <c r="C229" s="27" t="s">
-        <v>477</v>
       </c>
       <c r="D229" s="28"/>
       <c r="E229" s="29">
@@ -22644,10 +22656,10 @@
         <v>46287</v>
       </c>
       <c r="B230" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="C230" s="37" t="s">
         <v>476</v>
-      </c>
-      <c r="C230" s="37" t="s">
-        <v>478</v>
       </c>
       <c r="D230" s="38"/>
       <c r="E230" s="39">
@@ -22697,7 +22709,7 @@
       </c>
       <c r="B231" s="26"/>
       <c r="C231" s="27" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="D231" s="28">
         <v>3.5</v>
@@ -22749,7 +22761,7 @@
       </c>
       <c r="B232" s="36"/>
       <c r="C232" s="37" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D232" s="38">
         <v>31.5</v>
@@ -22800,10 +22812,10 @@
         <v>46290</v>
       </c>
       <c r="B233" s="26" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C233" s="27" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D233" s="28"/>
       <c r="E233" s="29">
@@ -22852,10 +22864,10 @@
         <v>46290</v>
       </c>
       <c r="B234" s="36" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="C234" s="37" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="D234" s="38"/>
       <c r="E234" s="39">
@@ -22904,10 +22916,10 @@
         <v>46290</v>
       </c>
       <c r="B235" s="26" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="C235" s="27" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D235" s="28"/>
       <c r="E235" s="29">
@@ -22956,10 +22968,10 @@
         <v>46290</v>
       </c>
       <c r="B236" s="36" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="C236" s="37" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="D236" s="38"/>
       <c r="E236" s="39">
@@ -23008,10 +23020,10 @@
         <v>46290</v>
       </c>
       <c r="B237" s="26" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C237" s="27" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="D237" s="28"/>
       <c r="E237" s="29">
@@ -23060,10 +23072,10 @@
         <v>46290</v>
       </c>
       <c r="B238" s="36" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="C238" s="37" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D238" s="38"/>
       <c r="E238" s="39">
@@ -23112,10 +23124,10 @@
         <v>46290</v>
       </c>
       <c r="B239" s="26" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C239" s="27" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D239" s="28"/>
       <c r="E239" s="29">
@@ -23164,10 +23176,10 @@
         <v>46290</v>
       </c>
       <c r="B240" s="36" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="C240" s="37" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D240" s="38"/>
       <c r="E240" s="39">
@@ -23217,7 +23229,7 @@
       </c>
       <c r="B241" s="26"/>
       <c r="C241" s="27" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D241" s="28">
         <v>6</v>
@@ -23262,18 +23274,30 @@
       </c>
     </row>
     <row r="242" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="25"/>
-      <c r="B242" s="36"/>
-      <c r="C242" s="37"/>
+      <c r="A242" s="25">
+        <v>46293</v>
+      </c>
+      <c r="B242" s="36" t="s">
+        <v>499</v>
+      </c>
+      <c r="C242" s="37" t="s">
+        <v>500</v>
+      </c>
       <c r="D242" s="38"/>
-      <c r="E242" s="39"/>
-      <c r="F242" s="136"/>
+      <c r="E242" s="39">
+        <v>37.5</v>
+      </c>
+      <c r="F242" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G242" s="40"/>
-      <c r="H242" s="41"/>
+      <c r="H242" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I242" s="42"/>
-      <c r="J242" s="43" t="str">
+      <c r="J242" s="43">
         <f>IF(AND(D242="",E242="",A242="",B242="",C242=""),"", IFERROR(IF(J241="",D2,J241),D2)+IF(E242="",0,E242)-IF(OR(G242="أبو اسحاق",G242="أبو آدم",G242="أبو اسحاق ",G242="أبو آدم "),0,IF(D242="",0,D242)))</f>
-        <v/>
+        <v>1557.0450000000001</v>
       </c>
       <c r="K242" s="44"/>
       <c r="L242" t="str">
@@ -23292,9 +23316,9 @@
         <f>IF(AND(D241&gt;0,F241="أحد الشركاء"),COUNTIFS($D$4:D241,"&gt;"&amp;0,$F$4:F241,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P242" t="str">
+      <c r="P242">
         <f>IF(OR($A242="",$F242="أحد الشركاء",AND($D242="",$E242="")),"",SUMPRODUCT(($A$4:$A242&lt;&gt;"")*($F$4:$F242&lt;&gt;"أحد الشركاء")*((($D$4:$D242&lt;&gt;"")+($E$4:$E242&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>218</v>
       </c>
       <c r="Q242" t="str">
         <f>IF(OR($A242="",$F242&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A242,"&lt;&gt;",$F$4:F242,"أحد الشركاء"))</f>
@@ -23302,23 +23326,33 @@
       </c>
     </row>
     <row r="243" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="25"/>
+      <c r="A243" s="25">
+        <v>46293</v>
+      </c>
       <c r="B243" s="26"/>
-      <c r="C243" s="27"/>
-      <c r="D243" s="28"/>
+      <c r="C243" s="27" t="s">
+        <v>501</v>
+      </c>
+      <c r="D243" s="28">
+        <v>20</v>
+      </c>
       <c r="E243" s="29"/>
-      <c r="F243" s="30"/>
+      <c r="F243" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G243" s="31"/>
-      <c r="H243" s="32"/>
+      <c r="H243" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I243" s="33"/>
-      <c r="J243" s="34" t="str">
+      <c r="J243" s="34">
         <f>IF(AND(D243="",E243="",A243="",B243="",C243=""),"", IFERROR(IF(J242="",D2,J242),D2)+IF(E243="",0,E243)-IF(OR(G243="أبو اسحاق",G243="أبو آدم",G243="أبو اسحاق ",G243="أبو آدم "),0,IF(D243="",0,D243)))</f>
-        <v/>
+        <v>1537.0450000000001</v>
       </c>
       <c r="K243" s="35"/>
-      <c r="L243" t="str">
+      <c r="L243">
         <f>IF(E242&gt;0,COUNTIF($E$4:E242,"&gt;0"),"")</f>
-        <v/>
+        <v>167</v>
       </c>
       <c r="M243" t="str">
         <f>IF(AND(D242&gt;0,G242="المحفظة"),COUNTIFS($D$4:D242,"&gt;"&amp;0,$G$4:G242,"المحفظة"),"")</f>
@@ -23332,9 +23366,9 @@
         <f>IF(AND(D242&gt;0,F242="أحد الشركاء"),COUNTIFS($D$4:D242,"&gt;"&amp;0,$F$4:F242,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P243" t="str">
+      <c r="P243">
         <f>IF(OR($A243="",$F243="أحد الشركاء",AND($D243="",$E243="")),"",SUMPRODUCT(($A$4:$A243&lt;&gt;"")*($F$4:$F243&lt;&gt;"أحد الشركاء")*((($D$4:$D243&lt;&gt;"")+($E$4:$E243&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>219</v>
       </c>
       <c r="Q243" t="str">
         <f>IF(OR($A243="",$F243&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A243,"&lt;&gt;",$F$4:F243,"أحد الشركاء"))</f>
@@ -23342,18 +23376,30 @@
       </c>
     </row>
     <row r="244" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="25"/>
+      <c r="A244" s="25">
+        <v>46293</v>
+      </c>
       <c r="B244" s="36"/>
-      <c r="C244" s="37"/>
-      <c r="D244" s="38"/>
+      <c r="C244" s="37" t="s">
+        <v>502</v>
+      </c>
+      <c r="D244" s="38">
+        <v>60</v>
+      </c>
       <c r="E244" s="39"/>
-      <c r="F244" s="136"/>
-      <c r="G244" s="40"/>
-      <c r="H244" s="41"/>
+      <c r="F244" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G244" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H244" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I244" s="42"/>
-      <c r="J244" s="43" t="str">
+      <c r="J244" s="43">
         <f>IF(AND(D244="",E244="",A244="",B244="",C244=""),"", IFERROR(IF(J243="",D2,J243),D2)+IF(E244="",0,E244)-IF(OR(G244="أبو اسحاق",G244="أبو آدم",G244="أبو اسحاق ",G244="أبو آدم "),0,IF(D244="",0,D244)))</f>
-        <v/>
+        <v>1477.0450000000001</v>
       </c>
       <c r="K244" s="44"/>
       <c r="L244" t="str">
@@ -23372,9 +23418,9 @@
         <f>IF(AND(D243&gt;0,F243="أحد الشركاء"),COUNTIFS($D$4:D243,"&gt;"&amp;0,$F$4:F243,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P244" t="str">
+      <c r="P244">
         <f>IF(OR($A244="",$F244="أحد الشركاء",AND($D244="",$E244="")),"",SUMPRODUCT(($A$4:$A244&lt;&gt;"")*($F$4:$F244&lt;&gt;"أحد الشركاء")*((($D$4:$D244&lt;&gt;"")+($E$4:$E244&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>220</v>
       </c>
       <c r="Q244" t="str">
         <f>IF(OR($A244="",$F244&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A244,"&lt;&gt;",$F$4:F244,"أحد الشركاء"))</f>
@@ -23400,9 +23446,9 @@
         <f>IF(E244&gt;0,COUNTIF($E$4:E244,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M245" t="str">
+      <c r="M245">
         <f>IF(AND(D244&gt;0,G244="المحفظة"),COUNTIFS($D$4:D244,"&gt;"&amp;0,$G$4:G244,"المحفظة"),"")</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="N245" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A245)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A245)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A245&lt;&gt;""),IFERROR(MAX($N$4:N244),0)+1,"")</f>
@@ -23789,11 +23835,11 @@
       <c r="C255" s="137"/>
       <c r="D255" s="46">
         <f>SUM(D4:D253)</f>
-        <v>3768.8950000000004</v>
+        <v>3848.8950000000004</v>
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
-        <v>3506.94</v>
+        <v>3544.44</v>
       </c>
       <c r="F255" s="140">
         <f>COUNTIF(H4:H253,"معلق")</f>
@@ -31311,7 +31357,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="180" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32622,7 +32668,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="179" t="s">
+      <c r="A55" s="180" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32636,7 +32682,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="181" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33947,7 +33993,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="181" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -33970,7 +34016,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="180">
+      <c r="E108" s="181">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -33979,17 +34025,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8992895-B9D0-46C4-BA0E-FA5DCD20E51D}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2199DF-8DA6-481B-9977-71BC434D2E44}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2792,14 +2792,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3162,7 +3162,7 @@
       <c r="E2" s="155"/>
       <c r="F2" s="119">
         <f>F206</f>
-        <v>981.79500000000007</v>
+        <v>921.79500000000007</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -7876,11 +7876,11 @@
       </c>
       <c r="E185" s="124">
         <f>IFERROR(INDEX('كشف الحساب'!$D$4:$D$254,MATCH(180,'كشف الحساب'!$P$4:$P$254,0)),"")</f>
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="F185" s="125">
         <f t="shared" si="5"/>
-        <v>583.04500000000007</v>
+        <v>523.04500000000007</v>
       </c>
     </row>
     <row r="186" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="F186" s="125">
         <f t="shared" si="5"/>
-        <v>586.04500000000007</v>
+        <v>526.04500000000007</v>
       </c>
     </row>
     <row r="187" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="F187" s="125">
         <f t="shared" si="5"/>
-        <v>596.04500000000007</v>
+        <v>536.04500000000007</v>
       </c>
     </row>
     <row r="188" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7958,7 +7958,7 @@
       </c>
       <c r="F188" s="125">
         <f t="shared" si="5"/>
-        <v>606.04500000000007</v>
+        <v>546.04500000000007</v>
       </c>
     </row>
     <row r="189" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -7984,7 +7984,7 @@
       </c>
       <c r="F189" s="125">
         <f t="shared" si="5"/>
-        <v>616.04500000000007</v>
+        <v>556.04500000000007</v>
       </c>
     </row>
     <row r="190" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8010,7 +8010,7 @@
       </c>
       <c r="F190" s="125">
         <f t="shared" si="5"/>
-        <v>625.04500000000007</v>
+        <v>565.04500000000007</v>
       </c>
     </row>
     <row r="191" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="F191" s="125">
         <f t="shared" si="5"/>
-        <v>631.04500000000007</v>
+        <v>571.04500000000007</v>
       </c>
     </row>
     <row r="192" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8062,7 +8062,7 @@
       </c>
       <c r="F192" s="125">
         <f t="shared" si="5"/>
-        <v>661.04500000000007</v>
+        <v>601.04500000000007</v>
       </c>
     </row>
     <row r="193" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="F193" s="125">
         <f t="shared" si="5"/>
-        <v>668.54500000000007</v>
+        <v>608.54500000000007</v>
       </c>
     </row>
     <row r="194" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8114,7 +8114,7 @@
       </c>
       <c r="F194" s="125">
         <f t="shared" si="5"/>
-        <v>671.04500000000007</v>
+        <v>611.04500000000007</v>
       </c>
     </row>
     <row r="195" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8140,7 +8140,7 @@
       </c>
       <c r="F195" s="125">
         <f t="shared" si="5"/>
-        <v>678.54500000000007</v>
+        <v>618.54500000000007</v>
       </c>
     </row>
     <row r="196" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8166,7 +8166,7 @@
       </c>
       <c r="F196" s="125">
         <f t="shared" si="5"/>
-        <v>653.54500000000007</v>
+        <v>593.54500000000007</v>
       </c>
     </row>
     <row r="197" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="F197" s="125">
         <f t="shared" si="5"/>
-        <v>896.54500000000007</v>
+        <v>836.54500000000007</v>
       </c>
     </row>
     <row r="198" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8218,7 +8218,7 @@
       </c>
       <c r="F198" s="125">
         <f t="shared" si="5"/>
-        <v>877.79500000000007</v>
+        <v>817.79500000000007</v>
       </c>
     </row>
     <row r="199" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="F199" s="125">
         <f t="shared" ref="F199:F205" si="6">IF($A199="","",IF($F198="",0,$F198)+IF($D199="",0,$D199)-IF($E199="",0,$E199))</f>
-        <v>857.79500000000007</v>
+        <v>797.79500000000007</v>
       </c>
     </row>
     <row r="200" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="F200" s="125">
         <f t="shared" si="6"/>
-        <v>859.29500000000007</v>
+        <v>799.29500000000007</v>
       </c>
     </row>
     <row r="201" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="F201" s="125">
         <f t="shared" si="6"/>
-        <v>860.29500000000007</v>
+        <v>800.29500000000007</v>
       </c>
     </row>
     <row r="202" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="F202" s="125">
         <f t="shared" si="6"/>
-        <v>862.79500000000007</v>
+        <v>802.79500000000007</v>
       </c>
     </row>
     <row r="203" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8348,7 +8348,7 @@
       </c>
       <c r="F203" s="125">
         <f t="shared" si="6"/>
-        <v>935.29500000000007</v>
+        <v>875.29500000000007</v>
       </c>
     </row>
     <row r="204" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="F204" s="125">
         <f t="shared" si="6"/>
-        <v>936.79500000000007</v>
+        <v>876.79500000000007</v>
       </c>
     </row>
     <row r="205" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="F205" s="125">
         <f t="shared" si="6"/>
-        <v>981.79500000000007</v>
+        <v>921.79500000000007</v>
       </c>
     </row>
     <row r="206" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -8415,11 +8415,11 @@
       </c>
       <c r="E206" s="129">
         <f>SUM(E6:E205)</f>
-        <v>1946.395</v>
+        <v>2006.395</v>
       </c>
       <c r="F206" s="130">
         <f>IFERROR(LOOKUP(2,1/($F$6:$F$205&lt;&gt;""),$F$6:$F$205),0)</f>
-        <v>981.79500000000007</v>
+        <v>921.79500000000007</v>
       </c>
     </row>
     <row r="208" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -21302,7 +21302,7 @@
         <v>435</v>
       </c>
       <c r="D204" s="38">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="E204" s="39"/>
       <c r="F204" s="136" t="s">
@@ -21317,7 +21317,7 @@
       <c r="I204" s="42"/>
       <c r="J204" s="43">
         <f>IF(AND(D204="",E204="",A204="",B204="",C204=""),"", IFERROR(IF(J203="",D2,J203),D2)+IF(E204="",0,E204)-IF(OR(G204="أبو اسحاق",G204="أبو آدم",G204="أبو اسحاق ",G204="أبو آدم "),0,IF(D204="",0,D204)))</f>
-        <v>583.04500000000007</v>
+        <v>523.04500000000007</v>
       </c>
       <c r="K204" s="44"/>
       <c r="L204" t="str">
@@ -21369,7 +21369,7 @@
       <c r="I205" s="33"/>
       <c r="J205" s="34">
         <f>IF(AND(D205="",E205="",A205="",B205="",C205=""),"", IFERROR(IF(J204="",D2,J204),D2)+IF(E205="",0,E205)-IF(OR(G205="أبو اسحاق",G205="أبو آدم",G205="أبو اسحاق ",G205="أبو آدم "),0,IF(D205="",0,D205)))</f>
-        <v>586.04500000000007</v>
+        <v>526.04500000000007</v>
       </c>
       <c r="K205" s="35"/>
       <c r="L205" t="str">
@@ -21421,7 +21421,7 @@
       <c r="I206" s="42"/>
       <c r="J206" s="43">
         <f>IF(AND(D206="",E206="",A206="",B206="",C206=""),"", IFERROR(IF(J205="",D2,J205),D2)+IF(E206="",0,E206)-IF(OR(G206="أبو اسحاق",G206="أبو آدم",G206="أبو اسحاق ",G206="أبو آدم "),0,IF(D206="",0,D206)))</f>
-        <v>596.04500000000007</v>
+        <v>536.04500000000007</v>
       </c>
       <c r="K206" s="44"/>
       <c r="L206">
@@ -21473,7 +21473,7 @@
       <c r="I207" s="33"/>
       <c r="J207" s="34">
         <f>IF(AND(D207="",E207="",A207="",B207="",C207=""),"", IFERROR(IF(J206="",D2,J206),D2)+IF(E207="",0,E207)-IF(OR(G207="أبو اسحاق",G207="أبو آدم",G207="أبو اسحاق ",G207="أبو آدم "),0,IF(D207="",0,D207)))</f>
-        <v>606.04500000000007</v>
+        <v>546.04500000000007</v>
       </c>
       <c r="K207" s="35"/>
       <c r="L207">
@@ -21525,7 +21525,7 @@
       <c r="I208" s="42"/>
       <c r="J208" s="43">
         <f>IF(AND(D208="",E208="",A208="",B208="",C208=""),"", IFERROR(IF(J207="",D2,J207),D2)+IF(E208="",0,E208)-IF(OR(G208="أبو اسحاق",G208="أبو آدم",G208="أبو اسحاق ",G208="أبو آدم "),0,IF(D208="",0,D208)))</f>
-        <v>616.04500000000007</v>
+        <v>556.04500000000007</v>
       </c>
       <c r="K208" s="44"/>
       <c r="L208">
@@ -21577,7 +21577,7 @@
       <c r="I209" s="33"/>
       <c r="J209" s="34">
         <f>IF(AND(D209="",E209="",A209="",B209="",C209=""),"", IFERROR(IF(J208="",D2,J208),D2)+IF(E209="",0,E209)-IF(OR(G209="أبو اسحاق",G209="أبو آدم",G209="أبو اسحاق ",G209="أبو آدم "),0,IF(D209="",0,D209)))</f>
-        <v>625.04500000000007</v>
+        <v>565.04500000000007</v>
       </c>
       <c r="K209" s="168" t="s">
         <v>498</v>
@@ -21631,7 +21631,7 @@
       <c r="I210" s="42"/>
       <c r="J210" s="43">
         <f>IF(AND(D210="",E210="",A210="",B210="",C210=""),"", IFERROR(IF(J209="",D2,J209),D2)+IF(E210="",0,E210)-IF(OR(G210="أبو اسحاق",G210="أبو آدم",G210="أبو اسحاق ",G210="أبو آدم "),0,IF(D210="",0,D210)))</f>
-        <v>631.04500000000007</v>
+        <v>571.04500000000007</v>
       </c>
       <c r="K210" s="169"/>
       <c r="L210">
@@ -21683,7 +21683,7 @@
       <c r="I211" s="33"/>
       <c r="J211" s="34">
         <f>IF(AND(D211="",E211="",A211="",B211="",C211=""),"", IFERROR(IF(J210="",D2,J210),D2)+IF(E211="",0,E211)-IF(OR(G211="أبو اسحاق",G211="أبو آدم",G211="أبو اسحاق ",G211="أبو آدم "),0,IF(D211="",0,D211)))</f>
-        <v>661.04500000000007</v>
+        <v>601.04500000000007</v>
       </c>
       <c r="K211" s="169"/>
       <c r="L211">
@@ -21735,7 +21735,7 @@
       <c r="I212" s="42"/>
       <c r="J212" s="43">
         <f>IF(AND(D212="",E212="",A212="",B212="",C212=""),"", IFERROR(IF(J211="",D2,J211),D2)+IF(E212="",0,E212)-IF(OR(G212="أبو اسحاق",G212="أبو آدم",G212="أبو اسحاق ",G212="أبو آدم "),0,IF(D212="",0,D212)))</f>
-        <v>668.54500000000007</v>
+        <v>608.54500000000007</v>
       </c>
       <c r="K212" s="169"/>
       <c r="L212">
@@ -21787,7 +21787,7 @@
       <c r="I213" s="33"/>
       <c r="J213" s="34">
         <f>IF(AND(D213="",E213="",A213="",B213="",C213=""),"", IFERROR(IF(J212="",D2,J212),D2)+IF(E213="",0,E213)-IF(OR(G213="أبو اسحاق",G213="أبو آدم",G213="أبو اسحاق ",G213="أبو آدم "),0,IF(D213="",0,D213)))</f>
-        <v>671.04500000000007</v>
+        <v>611.04500000000007</v>
       </c>
       <c r="K213" s="169"/>
       <c r="L213">
@@ -21839,7 +21839,7 @@
       <c r="I214" s="42"/>
       <c r="J214" s="43">
         <f>IF(AND(D214="",E214="",A214="",B214="",C214=""),"", IFERROR(IF(J213="",D2,J213),D2)+IF(E214="",0,E214)-IF(OR(G214="أبو اسحاق",G214="أبو آدم",G214="أبو اسحاق ",G214="أبو آدم "),0,IF(D214="",0,D214)))</f>
-        <v>678.54500000000007</v>
+        <v>618.54500000000007</v>
       </c>
       <c r="K214" s="170"/>
       <c r="L214">
@@ -21891,7 +21891,7 @@
       <c r="I215" s="33"/>
       <c r="J215" s="34">
         <f>IF(AND(D215="",E215="",A215="",B215="",C215=""),"", IFERROR(IF(J214="",D2,J214),D2)+IF(E215="",0,E215)-IF(OR(G215="أبو اسحاق",G215="أبو آدم",G215="أبو اسحاق ",G215="أبو آدم "),0,IF(D215="",0,D215)))</f>
-        <v>653.54500000000007</v>
+        <v>593.54500000000007</v>
       </c>
       <c r="K215" s="35"/>
       <c r="L215">
@@ -21943,7 +21943,7 @@
       <c r="I216" s="42"/>
       <c r="J216" s="43">
         <f>IF(AND(D216="",E216="",A216="",B216="",C216=""),"", IFERROR(IF(J215="",D2,J215),D2)+IF(E216="",0,E216)-IF(OR(G216="أبو اسحاق",G216="أبو آدم",G216="أبو اسحاق ",G216="أبو آدم "),0,IF(D216="",0,D216)))</f>
-        <v>896.54500000000007</v>
+        <v>836.54500000000007</v>
       </c>
       <c r="K216" s="44"/>
       <c r="L216" t="str">
@@ -21995,7 +21995,7 @@
       <c r="I217" s="33"/>
       <c r="J217" s="34">
         <f>IF(AND(D217="",E217="",A217="",B217="",C217=""),"", IFERROR(IF(J216="",D2,J216),D2)+IF(E217="",0,E217)-IF(OR(G217="أبو اسحاق",G217="أبو آدم",G217="أبو اسحاق ",G217="أبو آدم "),0,IF(D217="",0,D217)))</f>
-        <v>877.79500000000007</v>
+        <v>817.79500000000007</v>
       </c>
       <c r="K217" s="35"/>
       <c r="L217">
@@ -22047,7 +22047,7 @@
       <c r="I218" s="42"/>
       <c r="J218" s="43">
         <f>IF(AND(D218="",E218="",A218="",B218="",C218=""),"", IFERROR(IF(J217="",D2,J217),D2)+IF(E218="",0,E218)-IF(OR(G218="أبو اسحاق",G218="أبو آدم",G218="أبو اسحاق ",G218="أبو آدم "),0,IF(D218="",0,D218)))</f>
-        <v>857.79500000000007</v>
+        <v>797.79500000000007</v>
       </c>
       <c r="K218" s="44"/>
       <c r="L218" t="str">
@@ -22099,7 +22099,7 @@
       <c r="I219" s="33"/>
       <c r="J219" s="34">
         <f>IF(AND(D219="",E219="",A219="",B219="",C219=""),"", IFERROR(IF(J218="",D2,J218),D2)+IF(E219="",0,E219)-IF(OR(G219="أبو اسحاق",G219="أبو آدم",G219="أبو اسحاق ",G219="أبو آدم "),0,IF(D219="",0,D219)))</f>
-        <v>859.29500000000007</v>
+        <v>799.29500000000007</v>
       </c>
       <c r="K219" s="168" t="s">
         <v>497</v>
@@ -22153,7 +22153,7 @@
       <c r="I220" s="42"/>
       <c r="J220" s="43">
         <f>IF(AND(D220="",E220="",A220="",B220="",C220=""),"", IFERROR(IF(J219="",D2,J219),D2)+IF(E220="",0,E220)-IF(OR(G220="أبو اسحاق",G220="أبو آدم",G220="أبو اسحاق ",G220="أبو آدم "),0,IF(D220="",0,D220)))</f>
-        <v>860.29500000000007</v>
+        <v>800.29500000000007</v>
       </c>
       <c r="K220" s="169"/>
       <c r="L220">
@@ -22205,7 +22205,7 @@
       <c r="I221" s="33"/>
       <c r="J221" s="34">
         <f>IF(AND(D221="",E221="",A221="",B221="",C221=""),"", IFERROR(IF(J220="",D2,J220),D2)+IF(E221="",0,E221)-IF(OR(G221="أبو اسحاق",G221="أبو آدم",G221="أبو اسحاق ",G221="أبو آدم "),0,IF(D221="",0,D221)))</f>
-        <v>862.79500000000007</v>
+        <v>802.79500000000007</v>
       </c>
       <c r="K221" s="169"/>
       <c r="L221">
@@ -22257,7 +22257,7 @@
       <c r="I222" s="42"/>
       <c r="J222" s="43">
         <f>IF(AND(D222="",E222="",A222="",B222="",C222=""),"", IFERROR(IF(J221="",D2,J221),D2)+IF(E222="",0,E222)-IF(OR(G222="أبو اسحاق",G222="أبو آدم",G222="أبو اسحاق ",G222="أبو آدم "),0,IF(D222="",0,D222)))</f>
-        <v>935.29500000000007</v>
+        <v>875.29500000000007</v>
       </c>
       <c r="K222" s="169"/>
       <c r="L222">
@@ -22309,7 +22309,7 @@
       <c r="I223" s="33"/>
       <c r="J223" s="34">
         <f>IF(AND(D223="",E223="",A223="",B223="",C223=""),"", IFERROR(IF(J222="",D2,J222),D2)+IF(E223="",0,E223)-IF(OR(G223="أبو اسحاق",G223="أبو آدم",G223="أبو اسحاق ",G223="أبو آدم "),0,IF(D223="",0,D223)))</f>
-        <v>936.79500000000007</v>
+        <v>876.79500000000007</v>
       </c>
       <c r="K223" s="170"/>
       <c r="L223">
@@ -22361,7 +22361,7 @@
       <c r="I224" s="42"/>
       <c r="J224" s="43">
         <f>IF(AND(D224="",E224="",A224="",B224="",C224=""),"", IFERROR(IF(J223="",D2,J223),D2)+IF(E224="",0,E224)-IF(OR(G224="أبو اسحاق",G224="أبو آدم",G224="أبو اسحاق ",G224="أبو آدم "),0,IF(D224="",0,D224)))</f>
-        <v>981.79500000000007</v>
+        <v>921.79500000000007</v>
       </c>
       <c r="K224" s="44"/>
       <c r="L224">
@@ -22413,7 +22413,7 @@
       <c r="I225" s="33"/>
       <c r="J225" s="34">
         <f>IF(AND(D225="",E225="",A225="",B225="",C225=""),"", IFERROR(IF(J224="",D2,J224),D2)+IF(E225="",0,E225)-IF(OR(G225="أبو اسحاق",G225="أبو آدم",G225="أبو اسحاق ",G225="أبو آدم "),0,IF(D225="",0,D225)))</f>
-        <v>986.79500000000007</v>
+        <v>926.79500000000007</v>
       </c>
       <c r="K225" s="35"/>
       <c r="L225">
@@ -22465,7 +22465,7 @@
       <c r="I226" s="42"/>
       <c r="J226" s="43">
         <f>IF(AND(D226="",E226="",A226="",B226="",C226=""),"", IFERROR(IF(J225="",D2,J225),D2)+IF(E226="",0,E226)-IF(OR(G226="أبو اسحاق",G226="أبو آدم",G226="أبو اسحاق ",G226="أبو آدم "),0,IF(D226="",0,D226)))</f>
-        <v>996.79500000000007</v>
+        <v>936.79500000000007</v>
       </c>
       <c r="K226" s="44"/>
       <c r="L226">
@@ -22517,7 +22517,7 @@
       <c r="I227" s="33"/>
       <c r="J227" s="34">
         <f>IF(AND(D227="",E227="",A227="",B227="",C227=""),"", IFERROR(IF(J226="",D2,J226),D2)+IF(E227="",0,E227)-IF(OR(G227="أبو اسحاق",G227="أبو آدم",G227="أبو اسحاق ",G227="أبو آدم "),0,IF(D227="",0,D227)))</f>
-        <v>1016.7950000000001</v>
+        <v>956.79500000000007</v>
       </c>
       <c r="K227" s="168" t="s">
         <v>477</v>
@@ -22571,7 +22571,7 @@
       <c r="I228" s="42"/>
       <c r="J228" s="43">
         <f>IF(AND(D228="",E228="",A228="",B228="",C228=""),"", IFERROR(IF(J227="",D2,J227),D2)+IF(E228="",0,E228)-IF(OR(G228="أبو اسحاق",G228="أبو آدم",G228="أبو اسحاق ",G228="أبو آدم "),0,IF(D228="",0,D228)))</f>
-        <v>1025.7950000000001</v>
+        <v>965.79500000000007</v>
       </c>
       <c r="K228" s="169"/>
       <c r="L228">
@@ -22623,7 +22623,7 @@
       <c r="I229" s="33"/>
       <c r="J229" s="34">
         <f>IF(AND(D229="",E229="",A229="",B229="",C229=""),"", IFERROR(IF(J228="",D2,J228),D2)+IF(E229="",0,E229)-IF(OR(G229="أبو اسحاق",G229="أبو آدم",G229="أبو اسحاق ",G229="أبو آدم "),0,IF(D229="",0,D229)))</f>
-        <v>1049.7950000000001</v>
+        <v>989.79500000000007</v>
       </c>
       <c r="K229" s="169"/>
       <c r="L229">
@@ -22675,7 +22675,7 @@
       <c r="I230" s="42"/>
       <c r="J230" s="43">
         <f>IF(AND(D230="",E230="",A230="",B230="",C230=""),"", IFERROR(IF(J229="",D2,J229),D2)+IF(E230="",0,E230)-IF(OR(G230="أبو اسحاق",G230="أبو آدم",G230="أبو اسحاق ",G230="أبو آدم "),0,IF(D230="",0,D230)))</f>
-        <v>1062.7950000000001</v>
+        <v>1002.7950000000001</v>
       </c>
       <c r="K230" s="170"/>
       <c r="L230">
@@ -22727,7 +22727,7 @@
       <c r="I231" s="33"/>
       <c r="J231" s="34">
         <f>IF(AND(D231="",E231="",A231="",B231="",C231=""),"", IFERROR(IF(J230="",D2,J230),D2)+IF(E231="",0,E231)-IF(OR(G231="أبو اسحاق",G231="أبو آدم",G231="أبو اسحاق ",G231="أبو آدم "),0,IF(D231="",0,D231)))</f>
-        <v>1059.2950000000001</v>
+        <v>999.29500000000007</v>
       </c>
       <c r="K231" s="35"/>
       <c r="L231">
@@ -22779,7 +22779,7 @@
       <c r="I232" s="42"/>
       <c r="J232" s="43">
         <f>IF(AND(D232="",E232="",A232="",B232="",C232=""),"", IFERROR(IF(J231="",D2,J231),D2)+IF(E232="",0,E232)-IF(OR(G232="أبو اسحاق",G232="أبو آدم",G232="أبو اسحاق ",G232="أبو آدم "),0,IF(D232="",0,D232)))</f>
-        <v>1027.7950000000001</v>
+        <v>967.79500000000007</v>
       </c>
       <c r="K232" s="44"/>
       <c r="L232" t="str">
@@ -22831,7 +22831,7 @@
       <c r="I233" s="33"/>
       <c r="J233" s="34">
         <f>IF(AND(D233="",E233="",A233="",B233="",C233=""),"", IFERROR(IF(J232="",D2,J232),D2)+IF(E233="",0,E233)-IF(OR(G233="أبو اسحاق",G233="أبو آدم",G233="أبو اسحاق ",G233="أبو آدم "),0,IF(D233="",0,D233)))</f>
-        <v>1037.7950000000001</v>
+        <v>977.79500000000007</v>
       </c>
       <c r="K233" s="35"/>
       <c r="L233" t="str">
@@ -22883,7 +22883,7 @@
       <c r="I234" s="42"/>
       <c r="J234" s="43">
         <f>IF(AND(D234="",E234="",A234="",B234="",C234=""),"", IFERROR(IF(J233="",D2,J233),D2)+IF(E234="",0,E234)-IF(OR(G234="أبو اسحاق",G234="أبو آدم",G234="أبو اسحاق ",G234="أبو آدم "),0,IF(D234="",0,D234)))</f>
-        <v>1047.5450000000001</v>
+        <v>987.54500000000007</v>
       </c>
       <c r="K234" s="44"/>
       <c r="L234">
@@ -22935,7 +22935,7 @@
       <c r="I235" s="33"/>
       <c r="J235" s="34">
         <f>IF(AND(D235="",E235="",A235="",B235="",C235=""),"", IFERROR(IF(J234="",D2,J234),D2)+IF(E235="",0,E235)-IF(OR(G235="أبو اسحاق",G235="أبو آدم",G235="أبو اسحاق ",G235="أبو آدم "),0,IF(D235="",0,D235)))</f>
-        <v>1067.5450000000001</v>
+        <v>1007.5450000000001</v>
       </c>
       <c r="K235" s="35"/>
       <c r="L235">
@@ -22987,7 +22987,7 @@
       <c r="I236" s="42"/>
       <c r="J236" s="43">
         <f>IF(AND(D236="",E236="",A236="",B236="",C236=""),"", IFERROR(IF(J235="",D2,J235),D2)+IF(E236="",0,E236)-IF(OR(G236="أبو اسحاق",G236="أبو آدم",G236="أبو اسحاق ",G236="أبو آدم "),0,IF(D236="",0,D236)))</f>
-        <v>1082.5450000000001</v>
+        <v>1022.5450000000001</v>
       </c>
       <c r="K236" s="44"/>
       <c r="L236">
@@ -23039,7 +23039,7 @@
       <c r="I237" s="33"/>
       <c r="J237" s="34">
         <f>IF(AND(D237="",E237="",A237="",B237="",C237=""),"", IFERROR(IF(J236="",D2,J236),D2)+IF(E237="",0,E237)-IF(OR(G237="أبو اسحاق",G237="أبو آدم",G237="أبو اسحاق ",G237="أبو آدم "),0,IF(D237="",0,D237)))</f>
-        <v>1342.5450000000001</v>
+        <v>1282.5450000000001</v>
       </c>
       <c r="K237" s="35"/>
       <c r="L237">
@@ -23091,7 +23091,7 @@
       <c r="I238" s="42"/>
       <c r="J238" s="43">
         <f>IF(AND(D238="",E238="",A238="",B238="",C238=""),"", IFERROR(IF(J237="",D2,J237),D2)+IF(E238="",0,E238)-IF(OR(G238="أبو اسحاق",G238="أبو آدم",G238="أبو اسحاق ",G238="أبو آدم "),0,IF(D238="",0,D238)))</f>
-        <v>1344.0450000000001</v>
+        <v>1284.0450000000001</v>
       </c>
       <c r="K238" s="44"/>
       <c r="L238">
@@ -23143,7 +23143,7 @@
       <c r="I239" s="33"/>
       <c r="J239" s="34">
         <f>IF(AND(D239="",E239="",A239="",B239="",C239=""),"", IFERROR(IF(J238="",D2,J238),D2)+IF(E239="",0,E239)-IF(OR(G239="أبو اسحاق",G239="أبو آدم",G239="أبو اسحاق ",G239="أبو آدم "),0,IF(D239="",0,D239)))</f>
-        <v>1345.5450000000001</v>
+        <v>1285.5450000000001</v>
       </c>
       <c r="K239" s="35"/>
       <c r="L239">
@@ -23195,7 +23195,7 @@
       <c r="I240" s="42"/>
       <c r="J240" s="43">
         <f>IF(AND(D240="",E240="",A240="",B240="",C240=""),"", IFERROR(IF(J239="",D2,J239),D2)+IF(E240="",0,E240)-IF(OR(G240="أبو اسحاق",G240="أبو آدم",G240="أبو اسحاق ",G240="أبو آدم "),0,IF(D240="",0,D240)))</f>
-        <v>1525.5450000000001</v>
+        <v>1465.5450000000001</v>
       </c>
       <c r="K240" s="44"/>
       <c r="L240">
@@ -23245,7 +23245,7 @@
       <c r="I241" s="33"/>
       <c r="J241" s="34">
         <f>IF(AND(D241="",E241="",A241="",B241="",C241=""),"", IFERROR(IF(J240="",D2,J240),D2)+IF(E241="",0,E241)-IF(OR(G241="أبو اسحاق",G241="أبو آدم",G241="أبو اسحاق ",G241="أبو آدم "),0,IF(D241="",0,D241)))</f>
-        <v>1519.5450000000001</v>
+        <v>1459.5450000000001</v>
       </c>
       <c r="K241" s="35"/>
       <c r="L241">
@@ -23297,7 +23297,7 @@
       <c r="I242" s="42"/>
       <c r="J242" s="43">
         <f>IF(AND(D242="",E242="",A242="",B242="",C242=""),"", IFERROR(IF(J241="",D2,J241),D2)+IF(E242="",0,E242)-IF(OR(G242="أبو اسحاق",G242="أبو آدم",G242="أبو اسحاق ",G242="أبو آدم "),0,IF(D242="",0,D242)))</f>
-        <v>1557.0450000000001</v>
+        <v>1497.0450000000001</v>
       </c>
       <c r="K242" s="44"/>
       <c r="L242" t="str">
@@ -23347,7 +23347,7 @@
       <c r="I243" s="33"/>
       <c r="J243" s="34">
         <f>IF(AND(D243="",E243="",A243="",B243="",C243=""),"", IFERROR(IF(J242="",D2,J242),D2)+IF(E243="",0,E243)-IF(OR(G243="أبو اسحاق",G243="أبو آدم",G243="أبو اسحاق ",G243="أبو آدم "),0,IF(D243="",0,D243)))</f>
-        <v>1537.0450000000001</v>
+        <v>1477.0450000000001</v>
       </c>
       <c r="K243" s="35"/>
       <c r="L243">
@@ -23399,7 +23399,7 @@
       <c r="I244" s="42"/>
       <c r="J244" s="43">
         <f>IF(AND(D244="",E244="",A244="",B244="",C244=""),"", IFERROR(IF(J243="",D2,J243),D2)+IF(E244="",0,E244)-IF(OR(G244="أبو اسحاق",G244="أبو آدم",G244="أبو اسحاق ",G244="أبو آدم "),0,IF(D244="",0,D244)))</f>
-        <v>1477.0450000000001</v>
+        <v>1417.0450000000001</v>
       </c>
       <c r="K244" s="44"/>
       <c r="L244" t="str">
@@ -23835,7 +23835,7 @@
       <c r="C255" s="137"/>
       <c r="D255" s="46">
         <f>SUM(D4:D253)</f>
-        <v>3848.8950000000004</v>
+        <v>3908.8950000000004</v>
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
@@ -31357,7 +31357,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="179" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32668,7 +32668,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="180" t="s">
+      <c r="A55" s="179" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32682,7 +32682,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="179" t="s">
+      <c r="A56" s="181" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33993,7 +33993,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="179" t="s">
+      <c r="A107" s="181" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -34016,7 +34016,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="181">
+      <c r="E108" s="180">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -34025,17 +34025,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2199DF-8DA6-481B-9977-71BC434D2E44}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D6C75A-A8A6-471D-B6B9-CEFF5839507C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="504">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1551,6 +1551,9 @@
   </si>
   <si>
     <t>احواض عدد 3000 الحبه 20 فلس</t>
+  </si>
+  <si>
+    <t>بونص نزمول 20 + رواتب 420+50 كهرباء وماء</t>
   </si>
 </sst>
 </file>
@@ -2792,14 +2795,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23428,18 +23431,30 @@
       </c>
     </row>
     <row r="245" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="25"/>
+      <c r="A245" s="25">
+        <v>46284</v>
+      </c>
       <c r="B245" s="26"/>
-      <c r="C245" s="27"/>
-      <c r="D245" s="28"/>
+      <c r="C245" s="27" t="s">
+        <v>503</v>
+      </c>
+      <c r="D245" s="28">
+        <v>490</v>
+      </c>
       <c r="E245" s="29"/>
-      <c r="F245" s="30"/>
-      <c r="G245" s="31"/>
-      <c r="H245" s="32"/>
+      <c r="F245" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G245" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H245" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I245" s="33"/>
-      <c r="J245" s="34" t="str">
+      <c r="J245" s="34">
         <f>IF(AND(D245="",E245="",A245="",B245="",C245=""),"", IFERROR(IF(J244="",D2,J244),D2)+IF(E245="",0,E245)-IF(OR(G245="أبو اسحاق",G245="أبو آدم",G245="أبو اسحاق ",G245="أبو آدم "),0,IF(D245="",0,D245)))</f>
-        <v/>
+        <v>927.04500000000007</v>
       </c>
       <c r="K245" s="35"/>
       <c r="L245" t="str">
@@ -23458,9 +23473,9 @@
         <f>IF(AND(D244&gt;0,F244="أحد الشركاء"),COUNTIFS($D$4:D244,"&gt;"&amp;0,$F$4:F244,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P245" t="str">
+      <c r="P245">
         <f>IF(OR($A245="",$F245="أحد الشركاء",AND($D245="",$E245="")),"",SUMPRODUCT(($A$4:$A245&lt;&gt;"")*($F$4:$F245&lt;&gt;"أحد الشركاء")*((($D$4:$D245&lt;&gt;"")+($E$4:$E245&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>221</v>
       </c>
       <c r="Q245" t="str">
         <f>IF(OR($A245="",$F245&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A245,"&lt;&gt;",$F$4:F245,"أحد الشركاء"))</f>
@@ -23486,9 +23501,9 @@
         <f>IF(E245&gt;0,COUNTIF($E$4:E245,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M246" t="str">
+      <c r="M246">
         <f>IF(AND(D245&gt;0,G245="المحفظة"),COUNTIFS($D$4:D245,"&gt;"&amp;0,$G$4:G245,"المحفظة"),"")</f>
-        <v/>
+        <v>51</v>
       </c>
       <c r="N246" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A246)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A246)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A246&lt;&gt;""),IFERROR(MAX($N$4:N245),0)+1,"")</f>
@@ -23835,7 +23850,7 @@
       <c r="C255" s="137"/>
       <c r="D255" s="46">
         <f>SUM(D4:D253)</f>
-        <v>3908.8950000000004</v>
+        <v>4398.8950000000004</v>
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
@@ -31357,7 +31372,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="180" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32668,7 +32683,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="179" t="s">
+      <c r="A55" s="180" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32682,7 +32697,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="181" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -33993,7 +34008,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="181" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -34016,7 +34031,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="180">
+      <c r="E108" s="181">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -34025,17 +34040,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23D6C75A-A8A6-471D-B6B9-CEFF5839507C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8869BF5D-A805-471C-82B8-167B529E50B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1191" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="510">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1554,6 +1554,24 @@
   </si>
   <si>
     <t>بونص نزمول 20 + رواتب 420+50 كهرباء وماء</t>
+  </si>
+  <si>
+    <t>Inv-182</t>
+  </si>
+  <si>
+    <t>متنوع زهور التهاني</t>
+  </si>
+  <si>
+    <t>Inv-183</t>
+  </si>
+  <si>
+    <t>متنوع ايمن</t>
+  </si>
+  <si>
+    <t>Inv-184</t>
+  </si>
+  <si>
+    <t>متنوع ابوادم</t>
   </si>
 </sst>
 </file>
@@ -2795,14 +2813,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23483,18 +23501,30 @@
       </c>
     </row>
     <row r="246" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="25"/>
-      <c r="B246" s="36"/>
-      <c r="C246" s="37"/>
+      <c r="A246" s="25">
+        <v>46296</v>
+      </c>
+      <c r="B246" s="36" t="s">
+        <v>504</v>
+      </c>
+      <c r="C246" s="37" t="s">
+        <v>505</v>
+      </c>
       <c r="D246" s="38"/>
-      <c r="E246" s="39"/>
-      <c r="F246" s="136"/>
+      <c r="E246" s="39">
+        <v>290</v>
+      </c>
+      <c r="F246" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G246" s="40"/>
-      <c r="H246" s="41"/>
+      <c r="H246" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I246" s="42"/>
-      <c r="J246" s="43" t="str">
+      <c r="J246" s="43">
         <f>IF(AND(D246="",E246="",A246="",B246="",C246=""),"", IFERROR(IF(J245="",D2,J245),D2)+IF(E246="",0,E246)-IF(OR(G246="أبو اسحاق",G246="أبو آدم",G246="أبو اسحاق ",G246="أبو آدم "),0,IF(D246="",0,D246)))</f>
-        <v/>
+        <v>1217.0450000000001</v>
       </c>
       <c r="K246" s="44"/>
       <c r="L246" t="str">
@@ -23513,9 +23543,9 @@
         <f>IF(AND(D245&gt;0,F245="أحد الشركاء"),COUNTIFS($D$4:D245,"&gt;"&amp;0,$F$4:F245,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P246" t="str">
+      <c r="P246">
         <f>IF(OR($A246="",$F246="أحد الشركاء",AND($D246="",$E246="")),"",SUMPRODUCT(($A$4:$A246&lt;&gt;"")*($F$4:$F246&lt;&gt;"أحد الشركاء")*((($D$4:$D246&lt;&gt;"")+($E$4:$E246&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>222</v>
       </c>
       <c r="Q246" t="str">
         <f>IF(OR($A246="",$F246&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A246,"&lt;&gt;",$F$4:F246,"أحد الشركاء"))</f>
@@ -23523,23 +23553,35 @@
       </c>
     </row>
     <row r="247" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="25"/>
-      <c r="B247" s="26"/>
-      <c r="C247" s="27"/>
+      <c r="A247" s="25">
+        <v>46297</v>
+      </c>
+      <c r="B247" s="26" t="s">
+        <v>506</v>
+      </c>
+      <c r="C247" s="27" t="s">
+        <v>507</v>
+      </c>
       <c r="D247" s="28"/>
-      <c r="E247" s="29"/>
-      <c r="F247" s="30"/>
+      <c r="E247" s="29">
+        <v>105</v>
+      </c>
+      <c r="F247" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G247" s="31"/>
-      <c r="H247" s="32"/>
+      <c r="H247" s="32" t="s">
+        <v>50</v>
+      </c>
       <c r="I247" s="33"/>
-      <c r="J247" s="34" t="str">
+      <c r="J247" s="34">
         <f>IF(AND(D247="",E247="",A247="",B247="",C247=""),"", IFERROR(IF(J246="",D2,J246),D2)+IF(E247="",0,E247)-IF(OR(G247="أبو اسحاق",G247="أبو آدم",G247="أبو اسحاق ",G247="أبو آدم "),0,IF(D247="",0,D247)))</f>
-        <v/>
+        <v>1322.0450000000001</v>
       </c>
       <c r="K247" s="35"/>
-      <c r="L247" t="str">
+      <c r="L247">
         <f>IF(E246&gt;0,COUNTIF($E$4:E246,"&gt;0"),"")</f>
-        <v/>
+        <v>168</v>
       </c>
       <c r="M247" t="str">
         <f>IF(AND(D246&gt;0,G246="المحفظة"),COUNTIFS($D$4:D246,"&gt;"&amp;0,$G$4:G246,"المحفظة"),"")</f>
@@ -23553,9 +23595,9 @@
         <f>IF(AND(D246&gt;0,F246="أحد الشركاء"),COUNTIFS($D$4:D246,"&gt;"&amp;0,$F$4:F246,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P247" t="str">
+      <c r="P247">
         <f>IF(OR($A247="",$F247="أحد الشركاء",AND($D247="",$E247="")),"",SUMPRODUCT(($A$4:$A247&lt;&gt;"")*($F$4:$F247&lt;&gt;"أحد الشركاء")*((($D$4:$D247&lt;&gt;"")+($E$4:$E247&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>223</v>
       </c>
       <c r="Q247" t="str">
         <f>IF(OR($A247="",$F247&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A247,"&lt;&gt;",$F$4:F247,"أحد الشركاء"))</f>
@@ -23563,23 +23605,35 @@
       </c>
     </row>
     <row r="248" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="25"/>
-      <c r="B248" s="36"/>
-      <c r="C248" s="37"/>
+      <c r="A248" s="25">
+        <v>46297</v>
+      </c>
+      <c r="B248" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="C248" s="37" t="s">
+        <v>509</v>
+      </c>
       <c r="D248" s="38"/>
-      <c r="E248" s="39"/>
-      <c r="F248" s="136"/>
+      <c r="E248" s="39">
+        <v>48</v>
+      </c>
+      <c r="F248" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G248" s="40"/>
-      <c r="H248" s="41"/>
+      <c r="H248" s="41" t="s">
+        <v>50</v>
+      </c>
       <c r="I248" s="42"/>
-      <c r="J248" s="43" t="str">
+      <c r="J248" s="43">
         <f>IF(AND(D248="",E248="",A248="",B248="",C248=""),"", IFERROR(IF(J247="",D2,J247),D2)+IF(E248="",0,E248)-IF(OR(G248="أبو اسحاق",G248="أبو آدم",G248="أبو اسحاق ",G248="أبو آدم "),0,IF(D248="",0,D248)))</f>
-        <v/>
+        <v>1370.0450000000001</v>
       </c>
       <c r="K248" s="44"/>
-      <c r="L248" t="str">
+      <c r="L248">
         <f>IF(E247&gt;0,COUNTIF($E$4:E247,"&gt;0"),"")</f>
-        <v/>
+        <v>169</v>
       </c>
       <c r="M248" t="str">
         <f>IF(AND(D247&gt;0,G247="المحفظة"),COUNTIFS($D$4:D247,"&gt;"&amp;0,$G$4:G247,"المحفظة"),"")</f>
@@ -23593,9 +23647,9 @@
         <f>IF(AND(D247&gt;0,F247="أحد الشركاء"),COUNTIFS($D$4:D247,"&gt;"&amp;0,$F$4:F247,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P248" t="str">
+      <c r="P248">
         <f>IF(OR($A248="",$F248="أحد الشركاء",AND($D248="",$E248="")),"",SUMPRODUCT(($A$4:$A248&lt;&gt;"")*($F$4:$F248&lt;&gt;"أحد الشركاء")*((($D$4:$D248&lt;&gt;"")+($E$4:$E248&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>224</v>
       </c>
       <c r="Q248" t="str">
         <f>IF(OR($A248="",$F248&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A248,"&lt;&gt;",$F$4:F248,"أحد الشركاء"))</f>
@@ -23617,9 +23671,9 @@
         <v/>
       </c>
       <c r="K249" s="35"/>
-      <c r="L249" t="str">
+      <c r="L249">
         <f>IF(E248&gt;0,COUNTIF($E$4:E248,"&gt;0"),"")</f>
-        <v/>
+        <v>170</v>
       </c>
       <c r="M249" t="str">
         <f>IF(AND(D248&gt;0,G248="المحفظة"),COUNTIFS($D$4:D248,"&gt;"&amp;0,$G$4:G248,"المحفظة"),"")</f>
@@ -23854,11 +23908,11 @@
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
-        <v>3544.44</v>
+        <v>3987.44</v>
       </c>
       <c r="F255" s="140">
         <f>COUNTIF(H4:H253,"معلق")</f>
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G255" s="137"/>
       <c r="H255" s="137"/>
@@ -31372,7 +31426,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="179" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32683,7 +32737,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="180" t="s">
+      <c r="A55" s="179" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32697,7 +32751,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="179" t="s">
+      <c r="A56" s="181" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -34008,7 +34062,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="179" t="s">
+      <c r="A107" s="181" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -34031,7 +34085,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="181">
+      <c r="E108" s="180">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -34040,17 +34094,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8869BF5D-A805-471C-82B8-167B529E50B0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB842E9-BE94-4BF2-B46C-D540AA23FF32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="511">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1572,6 +1572,9 @@
   </si>
   <si>
     <t>متنوع ابوادم</t>
+  </si>
+  <si>
+    <t>كوكوبيت عدد 7 الحبه 3</t>
   </si>
 </sst>
 </file>
@@ -2813,14 +2816,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23657,18 +23660,30 @@
       </c>
     </row>
     <row r="249" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="25"/>
+      <c r="A249" s="25">
+        <v>46297</v>
+      </c>
       <c r="B249" s="26"/>
-      <c r="C249" s="27"/>
-      <c r="D249" s="28"/>
+      <c r="C249" s="27" t="s">
+        <v>510</v>
+      </c>
+      <c r="D249" s="28">
+        <v>21</v>
+      </c>
       <c r="E249" s="29"/>
-      <c r="F249" s="30"/>
-      <c r="G249" s="31"/>
-      <c r="H249" s="32"/>
+      <c r="F249" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="G249" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="H249" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I249" s="33"/>
-      <c r="J249" s="34" t="str">
+      <c r="J249" s="34">
         <f>IF(AND(D249="",E249="",A249="",B249="",C249=""),"", IFERROR(IF(J248="",D2,J248),D2)+IF(E249="",0,E249)-IF(OR(G249="أبو اسحاق",G249="أبو آدم",G249="أبو اسحاق ",G249="أبو آدم "),0,IF(D249="",0,D249)))</f>
-        <v/>
+        <v>1349.0450000000001</v>
       </c>
       <c r="K249" s="35"/>
       <c r="L249">
@@ -23687,9 +23702,9 @@
         <f>IF(AND(D248&gt;0,F248="أحد الشركاء"),COUNTIFS($D$4:D248,"&gt;"&amp;0,$F$4:F248,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P249" t="str">
+      <c r="P249">
         <f>IF(OR($A249="",$F249="أحد الشركاء",AND($D249="",$E249="")),"",SUMPRODUCT(($A$4:$A249&lt;&gt;"")*($F$4:$F249&lt;&gt;"أحد الشركاء")*((($D$4:$D249&lt;&gt;"")+($E$4:$E249&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>225</v>
       </c>
       <c r="Q249" t="str">
         <f>IF(OR($A249="",$F249&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A249,"&lt;&gt;",$F$4:F249,"أحد الشركاء"))</f>
@@ -23715,9 +23730,9 @@
         <f>IF(E249&gt;0,COUNTIF($E$4:E249,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M250" t="str">
+      <c r="M250">
         <f>IF(AND(D249&gt;0,G249="المحفظة"),COUNTIFS($D$4:D249,"&gt;"&amp;0,$G$4:G249,"المحفظة"),"")</f>
-        <v/>
+        <v>52</v>
       </c>
       <c r="N250" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A250)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A250)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A250&lt;&gt;""),IFERROR(MAX($N$4:N249),0)+1,"")</f>
@@ -23904,7 +23919,7 @@
       <c r="C255" s="137"/>
       <c r="D255" s="46">
         <f>SUM(D4:D253)</f>
-        <v>4398.8950000000004</v>
+        <v>4419.8950000000004</v>
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
@@ -31426,7 +31441,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="180" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32737,7 +32752,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="179" t="s">
+      <c r="A55" s="180" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32751,7 +32766,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="181" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -34062,7 +34077,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="181" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -34085,7 +34100,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="180">
+      <c r="E108" s="181">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -34094,17 +34109,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DB842E9-BE94-4BF2-B46C-D540AA23FF32}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21854E88-D03A-4CB0-8EF1-D64DCF2A8EAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1207" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="513">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1575,6 +1575,12 @@
   </si>
   <si>
     <t>كوكوبيت عدد 7 الحبه 3</t>
+  </si>
+  <si>
+    <t>Iknv-185</t>
+  </si>
+  <si>
+    <t>شجره بونسيانا</t>
   </si>
 </sst>
 </file>
@@ -2816,14 +2822,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23712,18 +23718,30 @@
       </c>
     </row>
     <row r="250" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="25"/>
-      <c r="B250" s="36"/>
-      <c r="C250" s="37"/>
+      <c r="A250" s="25">
+        <v>46298</v>
+      </c>
+      <c r="B250" s="36" t="s">
+        <v>511</v>
+      </c>
+      <c r="C250" s="37" t="s">
+        <v>512</v>
+      </c>
       <c r="D250" s="38"/>
-      <c r="E250" s="39"/>
-      <c r="F250" s="136"/>
+      <c r="E250" s="39">
+        <v>10</v>
+      </c>
+      <c r="F250" s="136" t="s">
+        <v>38</v>
+      </c>
       <c r="G250" s="40"/>
-      <c r="H250" s="41"/>
+      <c r="H250" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I250" s="42"/>
-      <c r="J250" s="43" t="str">
+      <c r="J250" s="43">
         <f>IF(AND(D250="",E250="",A250="",B250="",C250=""),"", IFERROR(IF(J249="",D2,J249),D2)+IF(E250="",0,E250)-IF(OR(G250="أبو اسحاق",G250="أبو آدم",G250="أبو اسحاق ",G250="أبو آدم "),0,IF(D250="",0,D250)))</f>
-        <v/>
+        <v>1359.0450000000001</v>
       </c>
       <c r="K250" s="44"/>
       <c r="L250" t="str">
@@ -23742,9 +23760,9 @@
         <f>IF(AND(D249&gt;0,F249="أحد الشركاء"),COUNTIFS($D$4:D249,"&gt;"&amp;0,$F$4:F249,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P250" t="str">
+      <c r="P250">
         <f>IF(OR($A250="",$F250="أحد الشركاء",AND($D250="",$E250="")),"",SUMPRODUCT(($A$4:$A250&lt;&gt;"")*($F$4:$F250&lt;&gt;"أحد الشركاء")*((($D$4:$D250&lt;&gt;"")+($E$4:$E250&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>226</v>
       </c>
       <c r="Q250" t="str">
         <f>IF(OR($A250="",$F250&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A250,"&lt;&gt;",$F$4:F250,"أحد الشركاء"))</f>
@@ -23766,9 +23784,9 @@
         <v/>
       </c>
       <c r="K251" s="35"/>
-      <c r="L251" t="str">
+      <c r="L251">
         <f>IF(E250&gt;0,COUNTIF($E$4:E250,"&gt;0"),"")</f>
-        <v/>
+        <v>171</v>
       </c>
       <c r="M251" t="str">
         <f>IF(AND(D250&gt;0,G250="المحفظة"),COUNTIFS($D$4:D250,"&gt;"&amp;0,$G$4:G250,"المحفظة"),"")</f>
@@ -23923,7 +23941,7 @@
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
-        <v>3987.44</v>
+        <v>3997.44</v>
       </c>
       <c r="F255" s="140">
         <f>COUNTIF(H4:H253,"معلق")</f>
@@ -31441,7 +31459,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="180" t="s">
+      <c r="A4" s="179" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32752,7 +32770,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="180" t="s">
+      <c r="A55" s="179" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32766,7 +32784,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="179" t="s">
+      <c r="A56" s="181" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -34077,7 +34095,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="179" t="s">
+      <c r="A107" s="181" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -34100,7 +34118,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="181">
+      <c r="E108" s="180">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -34109,17 +34127,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">

--- a/Farm_Account.xlsx
+++ b/Farm_Account.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hadi Ishak\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21854E88-D03A-4CB0-8EF1-D64DCF2A8EAE}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18ACFA4C-F6BC-44FA-95F9-6AAEF89F5DE6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="16380" windowHeight="8190" tabRatio="500" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1211" uniqueCount="513">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1219" uniqueCount="515">
   <si>
     <t>💰  محفظة مزرعة هادي إسحاق</t>
   </si>
@@ -1577,10 +1577,16 @@
     <t>كوكوبيت عدد 7 الحبه 3</t>
   </si>
   <si>
-    <t>Iknv-185</t>
-  </si>
-  <si>
     <t>شجره بونسيانا</t>
+  </si>
+  <si>
+    <t>Inv-185</t>
+  </si>
+  <si>
+    <t>Inv-186</t>
+  </si>
+  <si>
+    <t>اوليفيرا+حلفا</t>
   </si>
 </sst>
 </file>
@@ -2822,14 +2828,14 @@
     <xf numFmtId="0" fontId="26" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -23632,7 +23638,7 @@
       </c>
       <c r="G248" s="40"/>
       <c r="H248" s="41" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="I248" s="42"/>
       <c r="J248" s="43">
@@ -23722,10 +23728,10 @@
         <v>46298</v>
       </c>
       <c r="B250" s="36" t="s">
+        <v>512</v>
+      </c>
+      <c r="C250" s="37" t="s">
         <v>511</v>
-      </c>
-      <c r="C250" s="37" t="s">
-        <v>512</v>
       </c>
       <c r="D250" s="38"/>
       <c r="E250" s="39">
@@ -23770,18 +23776,30 @@
       </c>
     </row>
     <row r="251" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="25"/>
-      <c r="B251" s="26"/>
-      <c r="C251" s="27"/>
+      <c r="A251" s="25">
+        <v>46299</v>
+      </c>
+      <c r="B251" s="26" t="s">
+        <v>513</v>
+      </c>
+      <c r="C251" s="27" t="s">
+        <v>459</v>
+      </c>
       <c r="D251" s="28"/>
-      <c r="E251" s="29"/>
-      <c r="F251" s="30"/>
+      <c r="E251" s="29">
+        <v>26.25</v>
+      </c>
+      <c r="F251" s="30" t="s">
+        <v>38</v>
+      </c>
       <c r="G251" s="31"/>
-      <c r="H251" s="32"/>
+      <c r="H251" s="32" t="s">
+        <v>40</v>
+      </c>
       <c r="I251" s="33"/>
-      <c r="J251" s="34" t="str">
+      <c r="J251" s="34">
         <f>IF(AND(D251="",E251="",A251="",B251="",C251=""),"", IFERROR(IF(J250="",D2,J250),D2)+IF(E251="",0,E251)-IF(OR(G251="أبو اسحاق",G251="أبو آدم",G251="أبو اسحاق ",G251="أبو آدم "),0,IF(D251="",0,D251)))</f>
-        <v/>
+        <v>1385.2950000000001</v>
       </c>
       <c r="K251" s="35"/>
       <c r="L251">
@@ -23800,9 +23818,9 @@
         <f>IF(AND(D250&gt;0,F250="أحد الشركاء"),COUNTIFS($D$4:D250,"&gt;"&amp;0,$F$4:F250,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P251" t="str">
+      <c r="P251">
         <f>IF(OR($A251="",$F251="أحد الشركاء",AND($D251="",$E251="")),"",SUMPRODUCT(($A$4:$A251&lt;&gt;"")*($F$4:$F251&lt;&gt;"أحد الشركاء")*((($D$4:$D251&lt;&gt;"")+($E$4:$E251&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>227</v>
       </c>
       <c r="Q251" t="str">
         <f>IF(OR($A251="",$F251&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A251,"&lt;&gt;",$F$4:F251,"أحد الشركاء"))</f>
@@ -23810,23 +23828,35 @@
       </c>
     </row>
     <row r="252" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="25"/>
+      <c r="A252" s="25">
+        <v>46299</v>
+      </c>
       <c r="B252" s="36"/>
-      <c r="C252" s="37"/>
-      <c r="D252" s="38"/>
+      <c r="C252" s="37" t="s">
+        <v>514</v>
+      </c>
+      <c r="D252" s="38">
+        <v>24</v>
+      </c>
       <c r="E252" s="39"/>
-      <c r="F252" s="136"/>
-      <c r="G252" s="40"/>
-      <c r="H252" s="41"/>
+      <c r="F252" s="136" t="s">
+        <v>38</v>
+      </c>
+      <c r="G252" s="40" t="s">
+        <v>39</v>
+      </c>
+      <c r="H252" s="41" t="s">
+        <v>40</v>
+      </c>
       <c r="I252" s="42"/>
-      <c r="J252" s="43" t="str">
+      <c r="J252" s="43">
         <f>IF(AND(D252="",E252="",A252="",B252="",C252=""),"", IFERROR(IF(J251="",D2,J251),D2)+IF(E252="",0,E252)-IF(OR(G252="أبو اسحاق",G252="أبو آدم",G252="أبو اسحاق ",G252="أبو آدم "),0,IF(D252="",0,D252)))</f>
-        <v/>
+        <v>1361.2950000000001</v>
       </c>
       <c r="K252" s="44"/>
-      <c r="L252" t="str">
+      <c r="L252">
         <f>IF(E251&gt;0,COUNTIF($E$4:E251,"&gt;0"),"")</f>
-        <v/>
+        <v>172</v>
       </c>
       <c r="M252" t="str">
         <f>IF(AND(D251&gt;0,G251="المحفظة"),COUNTIFS($D$4:D251,"&gt;"&amp;0,$G$4:G251,"المحفظة"),"")</f>
@@ -23840,9 +23870,9 @@
         <f>IF(AND(D251&gt;0,F251="أحد الشركاء"),COUNTIFS($D$4:D251,"&gt;"&amp;0,$F$4:F251,"أحد الشركاء"),"")</f>
         <v/>
       </c>
-      <c r="P252" t="str">
+      <c r="P252">
         <f>IF(OR($A252="",$F252="أحد الشركاء",AND($D252="",$E252="")),"",SUMPRODUCT(($A$4:$A252&lt;&gt;"")*($F$4:$F252&lt;&gt;"أحد الشركاء")*((($D$4:$D252&lt;&gt;"")+($E$4:$E252&lt;&gt;""))&gt;0)))</f>
-        <v/>
+        <v>228</v>
       </c>
       <c r="Q252" t="str">
         <f>IF(OR($A252="",$F252&lt;&gt;"أحد الشركاء"),"",COUNTIFS($A$4:A252,"&lt;&gt;",$F$4:F252,"أحد الشركاء"))</f>
@@ -23868,9 +23898,9 @@
         <f>IF(E252&gt;0,COUNTIF($E$4:E252,"&gt;0"),"")</f>
         <v/>
       </c>
-      <c r="M253" t="str">
+      <c r="M253">
         <f>IF(AND(D252&gt;0,G252="المحفظة"),COUNTIFS($D$4:D252,"&gt;"&amp;0,$G$4:G252,"المحفظة"),"")</f>
-        <v/>
+        <v>53</v>
       </c>
       <c r="N253" t="str">
         <f>IF(AND(OR('طباعة كشف الحساب'!$C$2="الكل",MONTH(A253)=IFERROR(MATCH('طباعة كشف الحساب'!$C$2,{"يناير","فبراير","مارس","أبريل","مايو","يونيو","يوليو","أغسطس","سبتمبر","أكتوبر","نوفمبر","ديسمبر"},0),0)),OR('طباعة كشف الحساب'!$F$2="الكل",YEAR(A253)=IFERROR(VALUE('طباعة كشف الحساب'!$F$2),0)),A253&lt;&gt;""),IFERROR(MAX($N$4:N252),0)+1,"")</f>
@@ -23937,15 +23967,15 @@
       <c r="C255" s="137"/>
       <c r="D255" s="46">
         <f>SUM(D4:D253)</f>
-        <v>4419.8950000000004</v>
+        <v>4443.8950000000004</v>
       </c>
       <c r="E255" s="46">
         <f>SUM(E4:E253)</f>
-        <v>3997.44</v>
+        <v>4023.69</v>
       </c>
       <c r="F255" s="140">
         <f>COUNTIF(H4:H253,"معلق")</f>
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G255" s="137"/>
       <c r="H255" s="137"/>
@@ -31459,7 +31489,7 @@
       </c>
     </row>
     <row r="4" spans="1:7" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="179" t="s">
+      <c r="A4" s="180" t="s">
         <v>273</v>
       </c>
       <c r="B4" s="161"/>
@@ -32770,7 +32800,7 @@
       <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="179" t="s">
+      <c r="A55" s="180" t="s">
         <v>266</v>
       </c>
       <c r="B55" s="161"/>
@@ -32784,7 +32814,7 @@
       <c r="G55" s="76"/>
     </row>
     <row r="56" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="181" t="s">
+      <c r="A56" s="179" t="s">
         <v>275</v>
       </c>
       <c r="B56" s="161"/>
@@ -34095,7 +34125,7 @@
       <c r="G106" s="21"/>
     </row>
     <row r="107" spans="1:7" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="181" t="s">
+      <c r="A107" s="179" t="s">
         <v>276</v>
       </c>
       <c r="B107" s="161"/>
@@ -34118,7 +34148,7 @@
         <f>E55-D107</f>
         <v>0</v>
       </c>
-      <c r="E108" s="180">
+      <c r="E108" s="181">
         <f>SUM(E5:E107)</f>
         <v>0</v>
       </c>
@@ -34127,17 +34157,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A107:C107"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="D2:E2"/>
     <mergeCell ref="A108:C108"/>
     <mergeCell ref="D3:E3"/>
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="E108:G108"/>
     <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A107:C107"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="D2:E2"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation type="list" sqref="C2" xr:uid="{00000000-0002-0000-0500-000000000000}">
